--- a/sample-data/sample-run/selections/Ultimates.xlsx
+++ b/sample-data/sample-run/selections/Ultimates.xlsx
@@ -600,7 +600,7 @@
       </c>
       <c r="K2" s="9" t="inlineStr">
         <is>
-          <t>Incurred CL ultimate 3,163,774. Fully developed tail year (287 months, CDF 1.0). Incurred and Paid measurements converge; Incurred CL selected as primary method at full maturity. No meaningful IBNR. Reasonability: Loss ratio ~0.01 (extremely low, consistent with tail settlement pattern).</t>
+          <t>Selected 3,163,774. Tail maturity (age 287 months, CDF=1.00). Period is fully developed per both incurred and paid CDFs. Incurred CL equals the actual incurred value with zero IBNR, representing a fully closed book. Paid CL is slightly lower (3,042,295), consistent with some remaining case reserves on open claims. Incurred CL preferred as the more complete measure. IE and BF are irrelevant at 100% development. No prior selections available.</t>
         </is>
       </c>
       <c r="L2" s="10" t="n">
@@ -608,7 +608,7 @@
       </c>
       <c r="M2" s="10" t="inlineStr">
         <is>
-          <t>Fully matured (age 287). CL, IE, and BF all converge at 3.16M, actual equals ultimate. Zero IBNR across methods reflects complete development.</t>
+          <t>3,163,774 selected, matching Incurred CL (and IE/BF, all identical). At 287 months the year is fully developed; all methods agree and no IBNR remains. Paid CL of 3,042,295 is slightly lower but incurred is appropriate given full maturity. Zero uncertainty remains.</t>
         </is>
       </c>
       <c r="N2" s="11" t="n"/>
@@ -628,34 +628,34 @@
         <v>2199646.228088</v>
       </c>
       <c r="E3" s="8" t="n">
-        <v>2327910.728062187</v>
+        <v>2334716.957588959</v>
       </c>
       <c r="F3" s="8" t="n">
-        <v>2200568.611735119</v>
+        <v>2210644.45922844</v>
       </c>
       <c r="G3" s="8" t="n">
         <v>2904344.256599999</v>
       </c>
       <c r="H3" s="8" t="n">
-        <v>2327954.549521735</v>
+        <v>2336420.728174236</v>
       </c>
       <c r="I3" s="8" t="n">
-        <v>2200863.60419416</v>
+        <v>2214095.702001432</v>
       </c>
       <c r="J3" s="9" t="n">
-        <v>2327911</v>
+        <v>2297495</v>
       </c>
       <c r="K3" s="9" t="inlineStr">
         <is>
-          <t>Incurred CL ultimate 2,327,911. Nearly fully developed (275 months, CDF 1.0001, 99.99% developed). Incurred CL stable and credible. Paid CL shows similar development (1.0004). No material IBNR. Selected over IE (2,904,344) due to negative IBNR signal and stale a priori assumptions.</t>
+          <t>Selected 2,297,495. Tail maturity (age 275 months). Weighted 70% Incurred CL (2,334,717) + 30% Paid CL (2,210,644). IE disqualified (highly divergent from CL with implausible IBNR). BF near-identical to CL at this maturity. No prior selections.</t>
         </is>
       </c>
       <c r="L3" s="10" t="n">
-        <v>2327911</v>
+        <v>2334717</v>
       </c>
       <c r="M3" s="10" t="inlineStr">
         <is>
-          <t>Essentially mature (age 275). CL ultimate 2.33M selected; all methods clustered tightly (CL 2.33M, IE 2.90M, BF 2.33M). CL preferred given minimal tail risk and 99.99% developed.</t>
+          <t>2,334,717 selected, following Incurred CL at 275 months maturity (99.7% developed). CDF of 1.003 applies only a trivial tail. Paid CL of 2,210,644 is notably lower than incurred, suggesting some open reserves remain; incurred CL is the more reliable signal at this maturity. IE of 2,904,344 is implausibly high relative to actuals and not credible here.</t>
         </is>
       </c>
       <c r="N3" s="11" t="n"/>
@@ -675,34 +675,34 @@
         <v>1778091.575843999</v>
       </c>
       <c r="E4" s="8" t="n">
-        <v>1778419.63903829</v>
+        <v>1788776.128123245</v>
       </c>
       <c r="F4" s="8" t="n">
-        <v>1779826.221807177</v>
+        <v>1795916.943891835</v>
       </c>
       <c r="G4" s="8" t="n">
         <v>2633272.1256</v>
       </c>
       <c r="H4" s="8" t="n">
-        <v>1778577.332774477</v>
+        <v>1793820.393580948</v>
       </c>
       <c r="I4" s="8" t="n">
-        <v>1780658.003288799</v>
+        <v>1804228.110146753</v>
       </c>
       <c r="J4" s="9" t="n">
-        <v>1778420</v>
+        <v>1792346</v>
       </c>
       <c r="K4" s="9" t="inlineStr">
         <is>
-          <t>Incurred CL ultimate 1,778,420. Fully developed (263 months, CDF 1.0002, 99.98%). Incurred CL primary method at tail maturity. IE method shows 855k IBNR (stale a priori). Paid CL (1,779,826) shows convergence; Incurred selected for consistency. Loss ratio ~0.0054.</t>
+          <t>Selected 1,792,346. Tail maturity (age 263 months). Incurred CL (1,788,776) and Paid CL (1,795,917) converge within 0.4% — convergence rule applied, selecting midpoint. BF near-identical to CL at this maturity. No prior selections.</t>
         </is>
       </c>
       <c r="L4" s="10" t="n">
-        <v>1778420</v>
+        <v>1795917</v>
       </c>
       <c r="M4" s="10" t="inlineStr">
         <is>
-          <t>Mature (age 263). CL 1.78M selected. All methods converge (CL 1.78M, IE 2.63M, BF 1.78M). 99.98% developed; CL credible and low IBNR (328) affirms selection.</t>
+          <t>1,795,917 selected, following Paid CL at 263 months (99.0% developed). Incurred CL is 1,788,776 — essentially identical to paid (actual incurred and paid are both 1,778,092, implying reserves are near zero). Paid CL is preferred as it confirms no open case reserves inflating incurred. IE of 2,633,272 is far above actuals and lacks credibility at this maturity.</t>
         </is>
       </c>
       <c r="N4" s="11" t="n"/>
@@ -722,34 +722,34 @@
         <v>1122614.7306</v>
       </c>
       <c r="E5" s="8" t="n">
-        <v>1138429.08016653</v>
+        <v>1132748.604083724</v>
       </c>
       <c r="F5" s="8" t="n">
-        <v>1132250.110895177</v>
+        <v>1139538.287990636</v>
       </c>
       <c r="G5" s="8" t="n">
         <v>1678710.98</v>
       </c>
       <c r="H5" s="8" t="n">
-        <v>1145934.340684986</v>
+        <v>1137632.930247943</v>
       </c>
       <c r="I5" s="8" t="n">
-        <v>1136900.460000548</v>
+        <v>1147545.671413245</v>
       </c>
       <c r="J5" s="9" t="n">
-        <v>1138429</v>
+        <v>1136144</v>
       </c>
       <c r="K5" s="9" t="inlineStr">
         <is>
-          <t>Incurred CL ultimate 1,138,429. Late maturity (251 months, CDF 1.0141, 98.61% developed). Incurred CL primary. Paid CL (1,132,250) shows convergence within 0.5%. IE method inflated at 1,678,711 (negative IBNR indicates assumption stale). CL methods strongly preferred. Loss ratio ~0.0034.</t>
+          <t>Selected 1,136,144. Tail maturity (age 251 months). Incurred CL (1,132,749) and Paid CL (1,139,538) converge within 0.6% — convergence rule applied, selecting midpoint. BF near-identical to CL at this maturity. No prior selections.</t>
         </is>
       </c>
       <c r="L5" s="10" t="n">
-        <v>1138429</v>
+        <v>1132749</v>
       </c>
       <c r="M5" s="10" t="inlineStr">
         <is>
-          <t>Approaching mid-tail (age 251). CL 1.14M selected with modest development (CDF 1.014). Modest 15.8K IBNR. IE and BF slightly higher (1.68M and 1.15M) but CL reflects core development pattern.</t>
+          <t>1,132,749 selected, following Incurred CL at 251 months (99.1% developed). Incurred and Paid CL are nearly identical (1,132,749 vs 1,139,538) confirming stability. Actuals are the same for both measures indicating minimal open reserves. IE of 1,678,711 is far above actuals at near-full maturity and is disregarded.</t>
         </is>
       </c>
       <c r="N5" s="11" t="n"/>
@@ -769,34 +769,34 @@
         <v>2242149.132116</v>
       </c>
       <c r="E6" s="8" t="n">
-        <v>2273734.438445112</v>
+        <v>2269176.240088246</v>
       </c>
       <c r="F6" s="8" t="n">
-        <v>2278127.765863855</v>
+        <v>2287329.559604046</v>
       </c>
       <c r="G6" s="8" t="n">
         <v>1712285.2</v>
       </c>
       <c r="H6" s="8" t="n">
-        <v>2265935.134408242</v>
+        <v>2262543.368650875</v>
       </c>
       <c r="I6" s="8" t="n">
-        <v>2269191.373998036</v>
+        <v>2275971.008370179</v>
       </c>
       <c r="J6" s="9" t="n">
-        <v>2273734</v>
+        <v>2278253</v>
       </c>
       <c r="K6" s="9" t="inlineStr">
         <is>
-          <t>Incurred CL ultimate 2,273,734. Late maturity (239 months, CDF 1.0141, 98.61%). Incurred CL primary method selected. Paid CL convergence at 2,278,128 (0.2% difference). IE method fails fitness (negative 529k IBNR indicates a priori stale or unsupported). CL methods credible. Loss ratio ~0.0066.</t>
+          <t>Selected 2,278,253. Late maturity (age 239 months). Incurred CL (2,269,176) and Paid CL (2,287,330) converge within 0.8% — midpoint selected. IE disqualified (negative IBNR, stale a priori). BF (2,262,543) is secondary and confirms the CL range. No prior selections.</t>
         </is>
       </c>
       <c r="L6" s="10" t="n">
-        <v>2273734</v>
+        <v>2269176</v>
       </c>
       <c r="M6" s="10" t="inlineStr">
         <is>
-          <t>Early mid-tail (age 239). CL 2.27M selected. BF 2.27M and CL align well, while IE 1.71M appears below natural claims development due to negative IBNR (-530K), suggesting over-reservation in IE assumptions.</t>
+          <t>2,269,176 selected, following Incurred CL at 239 months (98.8% developed). This is a materially elevated year — incurred actual of 2,242,149 against an IE a priori of only 1,712,285, which produces a negative IBNR under IE and is clearly an artifact of a high-loss year exceeding the a priori. Paid CL of 2,287,330 agrees closely, confirming the CL indication is credible. BF of 2,262,543 also aligns. CL selected.</t>
         </is>
       </c>
       <c r="N6" s="11" t="n"/>
@@ -816,34 +816,34 @@
         <v>1462141.027856</v>
       </c>
       <c r="E7" s="8" t="n">
-        <v>1539015.844706935</v>
+        <v>1540538.342238185</v>
       </c>
       <c r="F7" s="8" t="n">
-        <v>1491099.997921647</v>
+        <v>1499061.921059408</v>
       </c>
       <c r="G7" s="8" t="n">
         <v>1746530.9035</v>
       </c>
       <c r="H7" s="8" t="n">
-        <v>1541898.514991141</v>
+        <v>1543600.61516261</v>
       </c>
       <c r="I7" s="8" t="n">
-        <v>1496060.775843178</v>
+        <v>1505156.916698673</v>
       </c>
       <c r="J7" s="9" t="n">
-        <v>1539016</v>
+        <v>1523948</v>
       </c>
       <c r="K7" s="9" t="inlineStr">
         <is>
-          <t>Incurred CL ultimate 1,539,016. Late maturity (227 months, CDF 1.0141, 98.61%). Incurred CL primary; Paid CL convergence at 1,491,100 (0.9% difference suggests data quality split). Incurred selected for consistency with prior periods. IE method shows divergence (1,746,531) with 229k IBNR; a priori fitness concerns. Loss ratio ~0.0044.</t>
+          <t>Selected 1,523,948. Late maturity (age 227 months). Weighted 60% Incurred CL (1,540,538) + 40% Paid CL (1,499,062). IE methods disqualified for implausible IBNR at this maturity. BF (1,543,601) secondary and consistent with CL range. No prior selections.</t>
         </is>
       </c>
       <c r="L7" s="10" t="n">
-        <v>1539016</v>
+        <v>1540538</v>
       </c>
       <c r="M7" s="10" t="inlineStr">
         <is>
-          <t>Mid-tail (age 227). CL 1.54M selected. CL and BF converge (1.54M and 1.54M); IE 1.75M shows minimal spread. CL modest IBNR (21K) is credible for this maturity.</t>
+          <t>1,540,538 selected, following Incurred CL at 227 months (98.5% developed). Paid CL at 1,499,062 is somewhat lower, reflecting modest open case reserves (incurred actual 1,517,637 vs paid 1,462,141). Both BF methods (1,543,601 incurred, 1,505,157 paid) bracket the CL selections. Incurred CL is the primary selection given high maturity; the small divergence between incurred and paid is within normal range.</t>
         </is>
       </c>
       <c r="N7" s="11" t="n"/>
@@ -863,34 +863,34 @@
         <v>4790693.153152</v>
       </c>
       <c r="E8" s="8" t="n">
-        <v>4878544.32188534</v>
+        <v>4898020.616126086</v>
       </c>
       <c r="F8" s="8" t="n">
-        <v>4885576.982394695</v>
+        <v>4936222.47941452</v>
       </c>
       <c r="G8" s="8" t="n">
         <v>2850338.4352</v>
       </c>
       <c r="H8" s="8" t="n">
-        <v>4850369.745669979</v>
+        <v>4861546.273480093</v>
       </c>
       <c r="I8" s="8" t="n">
-        <v>4846050.181880436</v>
+        <v>4874726.608658653</v>
       </c>
       <c r="J8" s="9" t="n">
-        <v>4878544</v>
+        <v>4917122</v>
       </c>
       <c r="K8" s="9" t="inlineStr">
         <is>
-          <t>Incurred CL ultimate 4,878,544. Late maturity (215 months, CDF 1.0141, 98.61%). Incurred CL primary method selected. Paid CL convergence at 4,885,577 (&lt;0.2% difference). IE method fails fitness severely (negative 1.96M IBNR indicates gross a priori mismatch). CL methods credible and stable. Loss ratio ~0.0139.</t>
+          <t>Selected 4,917,122. Late maturity (age 215 months). Incurred CL (4,898,021) and Paid CL (4,936,222) converge within 0.8% — midpoint selected. IE disqualified (negative IBNR, stale a priori). BF (4,861,546) is secondary and confirms the CL range. No prior selections.</t>
         </is>
       </c>
       <c r="L8" s="10" t="n">
-        <v>4878544</v>
+        <v>4898021</v>
       </c>
       <c r="M8" s="10" t="inlineStr">
         <is>
-          <t>Mid-tail (age 215). CL 4.88M selected with CDF 1.014. BF close at 4.85M. IE 2.85M appears artificially low with severe negative IBNR (-1.96M), indicating faulty IE reserve assumption. Actual 4.81M supports strong development.</t>
+          <t>4,898,021 selected, following Incurred CL at 215 months (98.2% developed). This is a very large-loss year with incurred actual of 4,810,775 — roughly 3-4x the typical year. IE of 2,850,338 and BF of 4,861,546 are far below the actual, confirming the a priori badly underestimates this year. The CL development factor is minimal (1.018), so the CL ultimate is essentially the actual. Paid CL of 4,936,222 is close. Incurred CL selected.</t>
         </is>
       </c>
       <c r="N8" s="11" t="n"/>
@@ -910,34 +910,34 @@
         <v>1378427.939547998</v>
       </c>
       <c r="E9" s="8" t="n">
-        <v>1398964.223832276</v>
+        <v>1407636.755688367</v>
       </c>
       <c r="F9" s="8" t="n">
-        <v>1408259.211377509</v>
+        <v>1427402.652966397</v>
       </c>
       <c r="G9" s="8" t="n">
         <v>2543927.0535</v>
       </c>
       <c r="H9" s="8" t="n">
-        <v>1415771.860342506</v>
+        <v>1431215.064692266</v>
       </c>
       <c r="I9" s="8" t="n">
-        <v>1432316.157593577</v>
+        <v>1465711.018463087</v>
       </c>
       <c r="J9" s="9" t="n">
-        <v>1398964</v>
+        <v>1417520</v>
       </c>
       <c r="K9" s="9" t="inlineStr">
         <is>
-          <t>Incurred CL ultimate 1,398,964. Late maturity (203 months, CDF 1.0149, 98.53%). Incurred CL primary. Paid CL convergence at 1,408,259 (0.7%). IE method shows divergence (2,543,927) and positive IBNR (1.16M) indicating a priori overstates; fitness concern. CL methods more credible. Loss ratio ~0.0038.</t>
+          <t>Selected 1,417,520. Late maturity (age 203 months). Incurred CL (1,407,637) and Paid CL (1,427,403) converge within 1.4% — midpoint selected. BF (1,431,215) is secondary and confirms the CL range. No prior selections.</t>
         </is>
       </c>
       <c r="L9" s="10" t="n">
-        <v>1398964</v>
+        <v>1427403</v>
       </c>
       <c r="M9" s="10" t="inlineStr">
         <is>
-          <t>Mid-tail (age 203). CL 1.40M selected (CDF 1.015). BF 1.42M aligns closely. IE 2.54M with large positive IBNR (1.17M) suggests over-conservative assumptions. CL-BF consensus favored.</t>
+          <t>1,427,403 selected, following Paid CL at 203 months (96.6% developed). Incurred CL of 1,407,637 is slightly lower; both measures show the same actual (1,378,428), meaning all open reserves are on paid basis. Paid BF of 1,465,711 and Incurred BF of 1,431,215 support the range. Paid CL is chosen as a modest check on any case reserve strengthening; all indications are in a narrow band.</t>
         </is>
       </c>
       <c r="N9" s="11" t="n"/>
@@ -957,34 +957,34 @@
         <v>1169581.089256</v>
       </c>
       <c r="E10" s="8" t="n">
-        <v>1195671.045826143</v>
+        <v>1197947.544886707</v>
       </c>
       <c r="F10" s="8" t="n">
-        <v>1196326.469521013</v>
+        <v>1217191.278030705</v>
       </c>
       <c r="G10" s="8" t="n">
         <v>2594805.5945</v>
       </c>
       <c r="H10" s="8" t="n">
-        <v>1226200.646537069</v>
+        <v>1231024.044818512</v>
       </c>
       <c r="I10" s="8" t="n">
-        <v>1227591.226210063</v>
+        <v>1271076.381259471</v>
       </c>
       <c r="J10" s="9" t="n">
-        <v>1195671</v>
+        <v>1207570</v>
       </c>
       <c r="K10" s="9" t="inlineStr">
         <is>
-          <t>Incurred CL ultimate 1,195,671. Late maturity (191 months, CDF 1.0223, 97.82%). Incurred CL primary method. Paid CL convergence at 1,196,326 (&lt;0.1%). IE method divergent (2,594,806) with positive 1.43M IBNR; a priori credibility low. CL methods strongly preferred. Loss ratio ~0.0032.</t>
+          <t>Selected 1,207,570. Late maturity (age 191 months). Incurred CL (1,197,948) and Paid CL (1,217,191) converge within 1.6% — midpoint selected. BF (1,231,024) is secondary and confirms the CL range. No prior selections.</t>
         </is>
       </c>
       <c r="L10" s="10" t="n">
-        <v>1195671</v>
+        <v>1217191</v>
       </c>
       <c r="M10" s="10" t="inlineStr">
         <is>
-          <t>Mid-tail (age 191). CL 1.20M selected (CDF 1.022). BF 1.23M similar. IE 2.59M with +1.43M IBNR appears overstated relative to claims gravity. CL modest IBNR (26K) credible.</t>
+          <t>1,217,191 selected, following Paid CL at 191 months (96.1% developed). Incurred CL of 1,197,948 is slightly lower. Actuals are identical for both measures (1,169,581), and CDFs are small. IE of 2,594,806 is far above actuals reflecting a low-loss year vs a priori — disregarded at this maturity. BF indications of 1,231,024 (incurred) and 1,271,076 (paid) are modestly above. Selecting paid CL as the anchor given high maturity.</t>
         </is>
       </c>
       <c r="N10" s="11" t="n"/>
@@ -1004,34 +1004,34 @@
         <v>1277672.072084001</v>
       </c>
       <c r="E11" s="8" t="n">
-        <v>1311397.917384093</v>
+        <v>1312586.094621001</v>
       </c>
       <c r="F11" s="8" t="n">
-        <v>1323094.647831844</v>
+        <v>1333006.53105774</v>
       </c>
       <c r="G11" s="8" t="n">
         <v>1134300.7311</v>
       </c>
       <c r="H11" s="8" t="n">
-        <v>1306843.42463363</v>
+        <v>1307843.808209848</v>
       </c>
       <c r="I11" s="8" t="n">
-        <v>1316613.247580141</v>
+        <v>1324758.050889469</v>
       </c>
       <c r="J11" s="9" t="n">
-        <v>1311398</v>
+        <v>1322796</v>
       </c>
       <c r="K11" s="9" t="inlineStr">
         <is>
-          <t>Incurred CL ultimate 1,311,398. Late maturity (179 months, CDF 1.0264, 97.43%). Incurred CL primary at this maturity. Paid CL convergence at 1,323,095 (0.9%). IE method shows negative IBNR (143k) indicating a priori over-compensates. CL methods credible. Loss ratio ~0.0035.</t>
+          <t>Selected 1,322,796. Mid maturity (age 179 months). Incurred CL (1,312,586) and Paid CL (1,333,007) converge within 1.5% — midpoint selected. Incurred IE disqualified (negative IBNR). BF (1,307,844) consistent with selection. No prior selections.</t>
         </is>
       </c>
       <c r="L11" s="10" t="n">
-        <v>1311398</v>
+        <v>1312586</v>
       </c>
       <c r="M11" s="10" t="inlineStr">
         <is>
-          <t>Mid-tail (age 179). CL 1.31M selected (CDF 1.026). BF 1.31M aligned. IE 1.13M with negative IBNR (-143K) and lowest indication suggests structural issue in assumptions. CL preferred.</t>
+          <t>1,312,586 selected, following Incurred CL at 179 months (97.3% developed). Paid CL of 1,333,007 is slightly above. IE of 1,134,301 is below actuals (low-loss year relative to a priori). BF methods of 1,307,844 (incurred) and 1,324,758 (paid) are close to CL. With 97%+ development, CL is highly credible; incurred CL selected given its slightly lower leverage and high maturity.</t>
         </is>
       </c>
       <c r="N11" s="11" t="n"/>
@@ -1051,34 +1051,34 @@
         <v>1892658.297732</v>
       </c>
       <c r="E12" s="8" t="n">
-        <v>1970985.739599864</v>
+        <v>1988125.368394688</v>
       </c>
       <c r="F12" s="8" t="n">
-        <v>1972291.924637652</v>
+        <v>1989436.782343472</v>
       </c>
       <c r="G12" s="8" t="n">
         <v>1542648.9944</v>
       </c>
       <c r="H12" s="8" t="n">
-        <v>1959053.908551951</v>
+        <v>1971982.621087207</v>
       </c>
       <c r="I12" s="8" t="n">
-        <v>1954944.581487382</v>
+        <v>1967702.26660322</v>
       </c>
       <c r="J12" s="9" t="n">
-        <v>1970986</v>
+        <v>1988781</v>
       </c>
       <c r="K12" s="9" t="inlineStr">
         <is>
-          <t>Incurred CL ultimate 1,970,986. Late maturity (167 months, CDF 1.0287, 97.21%). Incurred CL primary. Paid CL shows convergence at 1,972,292 (&lt;0.1%). IE method fails fitness (negative 373k IBNR). CL methods stable and credible. Incurred preferred for consistency. Loss ratio ~0.0051.</t>
+          <t>Selected 1,988,781. Mid maturity (age 167 months). Incurred CL (1,988,125) and Paid CL (1,989,437) converge within 0.1% — midpoint selected. Incurred IE disqualified (negative IBNR). BF (1,971,983) consistent with selection. No prior selections.</t>
         </is>
       </c>
       <c r="L12" s="10" t="n">
-        <v>1970986</v>
+        <v>1988125</v>
       </c>
       <c r="M12" s="10" t="inlineStr">
         <is>
-          <t>Mid-tail (age 167). CL 1.97M selected (CDF 1.029). BF 1.96M parallel. IE 1.54M with negative IBNR (-373K) again signals reserve over-statement. CL-BF consensus strong.</t>
+          <t>1,988,125 selected, following Incurred CL at 167 months (96.4% developed). Paid CL of 1,989,437 agrees almost exactly, which is reassuring. This is an elevated year vs a priori (IE of 1,542,649 would imply negative IBNR). BF indications of 1,971,983 (incurred) and 1,967,702 (paid) are also very close to CL. Strong convergence across all methods supports CL selection.</t>
         </is>
       </c>
       <c r="N12" s="11" t="n"/>
@@ -1098,34 +1098,34 @@
         <v>1194236.878339999</v>
       </c>
       <c r="E13" s="8" t="n">
-        <v>1402971.192188266</v>
+        <v>1422105.031111689</v>
       </c>
       <c r="F13" s="8" t="n">
-        <v>1250084.593172627</v>
+        <v>1267855.567590908</v>
       </c>
       <c r="G13" s="8" t="n">
         <v>1573501.9744</v>
       </c>
       <c r="H13" s="8" t="n">
-        <v>1407738.106958586</v>
+        <v>1428317.1331297</v>
       </c>
       <c r="I13" s="8" t="n">
-        <v>1264533.312705167</v>
+        <v>1285603.084278704</v>
       </c>
       <c r="J13" s="9" t="n">
-        <v>1402971</v>
+        <v>1368118</v>
       </c>
       <c r="K13" s="9" t="inlineStr">
         <is>
-          <t>Incurred CL ultimate 1,402,971. Late maturity (155 months, CDF 1.0288, 97.20%). Incurred CL primary. Paid CL convergence at 1,250,085 (0.4% divergence suggests minor data timing). Incurred selected for stability. IE method shows positive 209k IBNR but a priori credibility wanes at this maturity. Loss ratio ~0.0036.</t>
+          <t>Selected 1,368,118. Mid maturity (age 155 months). Weighted 65% Incurred CL (1,422,105) + 35% Paid CL (1,267,856). Incurred BF (1,428,317) within 4% of selection, confirming range. No prior selections.</t>
         </is>
       </c>
       <c r="L13" s="10" t="n">
-        <v>1402971</v>
+        <v>1422105</v>
       </c>
       <c r="M13" s="10" t="inlineStr">
         <is>
-          <t>Mid-tail (age 155). CL 1.40M selected (CDF 1.029). BF 1.41M very close. IE 1.57M with moderate IBNR (+210K) but higher than CL. CL conservative and supported by method agreement.</t>
+          <t>1,422,105 selected, following Incurred CL at 155 months (95.9% developed). Paid CL of 1,267,856 is notably lower, reflecting incurred actual of 1,363,753 vs paid actual of 1,194,237 — a meaningful gap suggesting open case reserves. At 155 months with a CDF of 1.043, incurred CL is more reliable as it captures open case development. Incurred BF of 1,428,317 agrees closely. Paid BF of 1,285,603 is higher than paid CL but still below incurred, consistent with the open reserve picture.</t>
         </is>
       </c>
       <c r="N13" s="11" t="n"/>
@@ -1145,34 +1145,34 @@
         <v>708529.9908599999</v>
       </c>
       <c r="E14" s="8" t="n">
-        <v>729196.934754035</v>
+        <v>742540.4765075424</v>
       </c>
       <c r="F14" s="8" t="n">
-        <v>742924.7660909795</v>
+        <v>763490.4060157106</v>
       </c>
       <c r="G14" s="8" t="n">
         <v>1203729.0102</v>
       </c>
       <c r="H14" s="8" t="n">
-        <v>742646.1517100412</v>
+        <v>763664.2354165952</v>
       </c>
       <c r="I14" s="8" t="n">
-        <v>764258.3642223282</v>
+        <v>795181.3038487363</v>
       </c>
       <c r="J14" s="9" t="n">
-        <v>729197</v>
+        <v>749872</v>
       </c>
       <c r="K14" s="9" t="inlineStr">
         <is>
-          <t>Incurred CL ultimate 729,197. Late-Mid maturity (143 months, CDF 1.0292, 97.17%). Incurred CL primary. Paid CL convergence at 742,925 (1.9% divergence). IE method shows large positive IBNR (495k) indicating a priori overstates; credibility low. CL methods preferred. Loss ratio ~0.0018.</t>
+          <t>Selected 749,872. Mid maturity (age 143 months). Weighted 65% Incurred CL (742,540) + 35% Paid CL (763,490). Incurred BF (763,664) within 2% of selection, confirming range. No prior selections.</t>
         </is>
       </c>
       <c r="L14" s="10" t="n">
-        <v>729197</v>
+        <v>742540</v>
       </c>
       <c r="M14" s="10" t="inlineStr">
         <is>
-          <t>Mid-tail (age 143). CL 0.73M selected (CDF 1.029). BF 0.74M near-identical. IE 1.20M with +495K IBNR appears inflated. CL modest IBNR (21K) and method convergence favored.</t>
+          <t>742,540 selected, following Incurred CL at 143 months (95.4% developed). Paid CL of 763,490 is close. Both actuals are 708,530 (same for incurred and paid), indicating minimal open reserves. BF methods of 763,664 (incurred) and 795,181 (paid) are slightly higher. IE of 1,203,729 is far above and not credible relative to actuals at this maturity. CL is the primary selection; incurred CL chosen.</t>
         </is>
       </c>
       <c r="N14" s="11" t="n"/>
@@ -1192,34 +1192,34 @@
         <v>1389603.684732</v>
       </c>
       <c r="E15" s="8" t="n">
-        <v>1436572.321458782</v>
+        <v>1499995.914631738</v>
       </c>
       <c r="F15" s="8" t="n">
-        <v>1476876.422218538</v>
+        <v>1512368.68741561</v>
       </c>
       <c r="G15" s="8" t="n">
         <v>1227803.5905</v>
       </c>
       <c r="H15" s="8" t="n">
-        <v>1429746.641652869</v>
+        <v>1479963.914991344</v>
       </c>
       <c r="I15" s="8" t="n">
-        <v>1462158.015498396</v>
+        <v>1489269.402712616</v>
       </c>
       <c r="J15" s="9" t="n">
-        <v>1436572</v>
+        <v>1506182</v>
       </c>
       <c r="K15" s="9" t="inlineStr">
         <is>
-          <t>Incurred CL ultimate 1,436,572. Late-Mid maturity (131 months, CDF 1.0338, 96.73%). Incurred CL primary. Paid CL shows convergence at 1,476,876 (2.8% divergence). IE method fails fitness (negative 161k IBNR). Incurred CL selected for data stability. Loss ratio ~0.0035.</t>
+          <t>Selected 1,506,182. Mid maturity (age 131 months). Incurred CL (1,499,996) and Paid CL (1,512,369) converge within 0.8% — midpoint selected. Incurred IE disqualified (negative IBNR). BF (1,479,964) consistent with selection. No prior selections.</t>
         </is>
       </c>
       <c r="L15" s="10" t="n">
-        <v>1436572</v>
+        <v>1499996</v>
       </c>
       <c r="M15" s="10" t="inlineStr">
         <is>
-          <t>Early-to-mid tail (age 131). CL 1.44M selected (CDF 1.034). BF 1.43M parallel. IE 1.23M with negative IBNR (-162K) below natural development. CL-BF consensus preferred.</t>
+          <t>1,499,996 selected, following Incurred CL at 131 months (92.6% developed). Paid CL of 1,512,369 is close. Both actuals are identical (1,389,604), and BF methods (1,479,964 incurred, 1,489,269 paid) are slightly below CL. IE of 1,227,804 implies negative IBNR — this is an elevated-loss year vs the a priori. All development methods agree within ~1%; incurred CL is the primary anchor with BF as a modest check.</t>
         </is>
       </c>
       <c r="N15" s="11" t="n"/>
@@ -1239,34 +1239,34 @@
         <v>3364231.298548001</v>
       </c>
       <c r="E16" s="8" t="n">
-        <v>3507099.955532203</v>
+        <v>3679098.836333144</v>
       </c>
       <c r="F16" s="8" t="n">
-        <v>3591250.926889994</v>
+        <v>3698059.893148677</v>
       </c>
       <c r="G16" s="8" t="n">
         <v>1669812.8832</v>
       </c>
       <c r="H16" s="8" t="n">
-        <v>3442067.663230833</v>
+        <v>3517368.726845768</v>
       </c>
       <c r="I16" s="8" t="n">
-        <v>3469787.915966828</v>
+        <v>3514967.442404812</v>
       </c>
       <c r="J16" s="9" t="n">
-        <v>3507100</v>
+        <v>3688580</v>
       </c>
       <c r="K16" s="9" t="inlineStr">
         <is>
-          <t>Incurred CL ultimate 3,507,100. Late-Mid maturity (119 months, CDF 1.0367, 96.46%). Incurred CL primary method selected. Paid CL shows convergence at 3,591,251 (2.4%). IE method fails fitness severely (negative 1.71M IBNR indicating gross a priori mismatch). CL methods credible. Loss ratio ~0.0084.</t>
+          <t>Selected 3,688,580. Early-mid maturity (age 119 months). Incurred CL (3,679,099) and Paid CL (3,698,060) converge within 0.5%. Incurred IE disqualified (negative IBNR). BF (3,517,369) and IE (1,669,813 if credible) consistent. No prior selections.</t>
         </is>
       </c>
       <c r="L16" s="10" t="n">
-        <v>3507100</v>
+        <v>3517369</v>
       </c>
       <c r="M16" s="10" t="inlineStr">
         <is>
-          <t>Early-to-mid tail (age 119). CL 3.51M selected (CDF 1.037). BF 3.44M very close. IE 1.67M with severely negative IBNR (-1.71M) indicates reserve assumption mismatch. Strong CL-BF alignment supports selection.</t>
+          <t>3,517,369 selected, following Incurred BF at 119 months (91.9% developed). This is a very elevated year — incurred actual of 3,382,963 with CL projecting 3,679,099 and IE implying a negative IBNR of -1.71M (a priori of 1,669,813 is far below actuals). The BF credibly blends the high actual with a modest development load: incurred BF at 3,517,369 is preferred over the CL at 3,679,099 as a tempering measure given the year's obvious outlier characteristics. Paid CL of 3,698,060 and paid BF of 3,514,967 bracket this selection. Selecting incurred BF.</t>
         </is>
       </c>
       <c r="N16" s="11" t="n"/>
@@ -1286,34 +1286,34 @@
         <v>2462208.676391999</v>
       </c>
       <c r="E17" s="8" t="n">
-        <v>2668446.238718787</v>
+        <v>2829297.908610753</v>
       </c>
       <c r="F17" s="8" t="n">
-        <v>2693017.112499169</v>
+        <v>2855389.845633978</v>
       </c>
       <c r="G17" s="8" t="n">
         <v>2554813.7112</v>
       </c>
       <c r="H17" s="8" t="n">
-        <v>2661542.445788538</v>
+        <v>2797964.576157609</v>
       </c>
       <c r="I17" s="8" t="n">
-        <v>2681172.215275716</v>
+        <v>2814001.14483584</v>
       </c>
       <c r="J17" s="9" t="n">
-        <v>2668446</v>
+        <v>2842344</v>
       </c>
       <c r="K17" s="9" t="inlineStr">
         <is>
-          <t>Incurred CL ultimate 2,668,446. Mid maturity (107 months, CDF 1.0647, 93.92%). Incurred CL primary; Paid CL shows elevated CDF (1.0937) and higher ultimate (2,693,017) suggesting paid data showing earlier volatility. Incurred selected for relative stability. BF (2,661,542) convergence near 99%. Loss ratio ~0.0063.</t>
+          <t>Selected 2,842,344. Early-mid maturity (age 107 months). Incurred CL (2,829,298) and Paid CL (2,855,390) converge within 0.9%. BF (2,797,965) and IE (2,554,814 if credible) consistent. No prior selections.</t>
         </is>
       </c>
       <c r="L17" s="10" t="n">
-        <v>2668446</v>
+        <v>2829298</v>
       </c>
       <c r="M17" s="10" t="inlineStr">
         <is>
-          <t>Mid-tail (age 107). CL 2.67M selected (CDF 1.065, elevated but justified by development pattern). BF 2.66M aligned. IE 2.55M with modest IBNR (+48K) but lower than CL. CL moderate tail capture suitable.</t>
+          <t>2,829,298 selected, following Incurred CL at 107 months (88.6% developed). Paid CL of 2,855,390 agrees closely. IE of 2,554,814 and incurred BF of 2,797,965 are modestly below CL. At 107 months, incurred CL is still highly credible and the spread between methods is modest (roughly 10%). The incurred CL is the primary selection as the book is well-developed at this age.</t>
         </is>
       </c>
       <c r="N17" s="11" t="n"/>
@@ -1333,34 +1333,34 @@
         <v>1205811.828916</v>
       </c>
       <c r="E18" s="8" t="n">
-        <v>1303580.950659252</v>
+        <v>1381615.222830049</v>
       </c>
       <c r="F18" s="8" t="n">
-        <v>1332824.875170461</v>
+        <v>1416542.270584225</v>
       </c>
       <c r="G18" s="8" t="n">
         <v>2605909.9854</v>
       </c>
       <c r="H18" s="8" t="n">
-        <v>1401256.178179987</v>
+        <v>1537400.401550151</v>
       </c>
       <c r="I18" s="8" t="n">
-        <v>1454144.953302083</v>
+        <v>1593477.325085412</v>
       </c>
       <c r="J18" s="9" t="n">
-        <v>1303581</v>
+        <v>1421504</v>
       </c>
       <c r="K18" s="9" t="inlineStr">
         <is>
-          <t>Incurred CL ultimate 1,303,581. Mid maturity (95 months, CDF 1.0811, 92.50%). Incurred CL primary method selected. Paid CL higher at 1,332,825 (2.2%) with elevated CDF (1.1053) indicating paid data volatility. Incurred more credible. BF shows 1,401,256 (7% higher); CL preferred given maturity. Loss ratio ~0.0029.</t>
+          <t>Selected 1,421,504. Early-mid maturity (age 95 months). Weighted 55% Incurred CL (1,381,615) + 25% Paid CL (1,416,542) + 20% Incurred BF (1,537,400). Incurred CL is primary at this maturity; BF provides a credibility check. No prior selections.</t>
         </is>
       </c>
       <c r="L18" s="10" t="n">
-        <v>1303581</v>
+        <v>1537400</v>
       </c>
       <c r="M18" s="10" t="inlineStr">
         <is>
-          <t>Early immature (age 95). CL 1.30M selected (CDF 1.081). BF 1.40M shows 195K IBNR premium. IE 2.61M with +1.4M IBNR seems excessive. CL balances incomplete development with modest tail.</t>
+          <t>1,537,400 selected, following Incurred BF at 95 months (87.3% developed). Incurred CL of 1,381,615 appears low relative to the a priori trend — the IE of 2,605,910 is very high but the actual of 1,205,812 is small, suggesting either a low-loss year or immature paid/incurred. Paid CL of 1,416,542 is close to incurred CL. Paid BF of 1,593,477 and incurred BF of 1,537,400 credibly temper the outlier CL direction. At 95 months with ~87% development, BF is the appropriate anchor. Selecting incurred BF as the primary indication.</t>
         </is>
       </c>
       <c r="N18" s="11" t="n"/>
@@ -1380,34 +1380,34 @@
         <v>2395448.423304001</v>
       </c>
       <c r="E19" s="8" t="n">
-        <v>2595631.406158274</v>
+        <v>2768026.838982237</v>
       </c>
       <c r="F19" s="8" t="n">
-        <v>2704433.006067339</v>
+        <v>2898504.960110452</v>
       </c>
       <c r="G19" s="8" t="n">
         <v>2215023.4875</v>
       </c>
       <c r="H19" s="8" t="n">
-        <v>2566277.766703072</v>
+        <v>2693592.187678146</v>
       </c>
       <c r="I19" s="8" t="n">
-        <v>2648517.405438418</v>
+        <v>2779881.798406536</v>
       </c>
       <c r="J19" s="9" t="n">
-        <v>2595631</v>
+        <v>2785760</v>
       </c>
       <c r="K19" s="9" t="inlineStr">
         <is>
-          <t>Incurred CL ultimate 2,595,631. Mid maturity (83 months, CDF 1.0836, 92.29%). Incurred CL primary; Paid CL higher at 2,704,433 (4.2%) with elevated tail factor (1.129). Incurred shows more stable development. IE shows negative IBNR (-180k); fitness concern. CL methods preferred. Loss ratio ~0.0058.</t>
+          <t>Selected 2,785,760. Early-mid maturity (age 83 months). Weighted 55% Incurred CL (2,768,027) + 25% Paid CL (2,898,505) + 20% Incurred BF (2,693,592). Incurred IE disqualified (negative IBNR, stale a priori). Paid IE disqualified (negative IBNR). Incurred CL is primary at this maturity; BF provides a credibility check. No prior selections.</t>
         </is>
       </c>
       <c r="L19" s="10" t="n">
-        <v>2595631</v>
+        <v>2768027</v>
       </c>
       <c r="M19" s="10" t="inlineStr">
         <is>
-          <t>Early immature (age 83). CL 2.60M selected (CDF 1.084, substantial tail). BF 2.57M close alignment. IE 2.22M with negative IBNR (-180K) inconsistent with development stage. CL captures real tail, BF confirms.</t>
+          <t>2,768,027 selected, following Incurred CL at 83 months (86.5% developed). Incurred actual is 2,395,448 with a modest development factor of 1.156. Paid CL of 2,898,505 is higher, reflecting a larger gap between incurred and paid actuals (2,395,448 vs 2,395,448 — same, but paid CDF is 1.21 vs incurred 1.156). Incurred BF of 2,693,592 and paid BF of 2,779,882 bracket the incurred CL. The IE a priori of 2,215,023 implies a negative IBNR, suggesting this is above the a priori. Incurred CL is the primary selection with BF as a check; selecting incurred CL.</t>
         </is>
       </c>
       <c r="N19" s="11" t="n"/>
@@ -1421,40 +1421,40 @@
         <v>71</v>
       </c>
       <c r="C20" s="8" t="n">
-        <v>2599882.874291999</v>
+        <v>2599882.874292</v>
       </c>
       <c r="D20" s="8" t="n">
         <v>2395189.834488001</v>
       </c>
       <c r="E20" s="8" t="n">
-        <v>3093230.752774115</v>
+        <v>3229577.567630864</v>
       </c>
       <c r="F20" s="8" t="n">
-        <v>2983478.834085414</v>
+        <v>3231484.153933392</v>
       </c>
       <c r="G20" s="8" t="n">
         <v>2259323.9575</v>
       </c>
       <c r="H20" s="8" t="n">
-        <v>2960228.664930736</v>
+        <v>3040400.024531793</v>
       </c>
       <c r="I20" s="8" t="n">
-        <v>2840688.363098005</v>
+        <v>2979893.240551207</v>
       </c>
       <c r="J20" s="9" t="n">
-        <v>3093231</v>
+        <v>3113619</v>
       </c>
       <c r="K20" s="9" t="inlineStr">
         <is>
-          <t>Incurred CL ultimate 3,093,231. Mid maturity (71 months, CDF 1.1898, 84.05% developed). Incurred CL selected. Paid CL elevated at 2,983,479 with lower CDF (1.2456); paid data shows earlier settlement activity. Incurred CL (1.19 CDF) more stable. BF at 2,960,229 convergence (95%). Incurred CL primary method. Loss ratio ~0.0069.</t>
+          <t>Selected 3,113,619. Green-to-early maturity (age 71 months). Weighted 35% Incurred BF (3,040,400) + 35% Incurred CL (3,229,578) + 20% Paid BF (2,979,893) + 10% Paid CL (3,231,484). Incurred IE disqualified (negative IBNR). Paid IE disqualified (negative IBNR). BF methods are primary at this maturity; CL provides a secondary check. No prior selections.</t>
         </is>
       </c>
       <c r="L20" s="10" t="n">
-        <v>2960229</v>
+        <v>3040400</v>
       </c>
       <c r="M20" s="10" t="inlineStr">
         <is>
-          <t>Immature (age 71). CL 3.09M selected (CDF 1.190, significant tail). BF 2.96M aligned and pragmatic. IE 2.26M with negative IBNR (-341K) contradicts early development expectations. CL-BF consensus reflects genuine tail risk at this maturity.</t>
+          <t>3,040,400 selected, following Incurred BF at 71 months (80.5% developed). Incurred CL of 3,229,578 and paid CL of 3,231,484 both indicate around 3.23M — elevated relative to the a priori IE of 2,259,324. At 71 months (~80% developed), CL carries moderate leverage and the BF appropriately tempers the indication. Incurred BF of 3,040,400 and paid BF of 2,979,893 are close; selecting incurred BF as it blends actual experience with a priori. The convergence of incurred and paid CL is reassuring that the underlying experience is real.</t>
         </is>
       </c>
       <c r="N20" s="11" t="n"/>
@@ -1468,40 +1468,40 @@
         <v>59</v>
       </c>
       <c r="C21" s="8" t="n">
-        <v>978899.5094679999</v>
+        <v>978899.509468</v>
       </c>
       <c r="D21" s="8" t="n">
-        <v>976050.8625559999</v>
+        <v>976050.862556</v>
       </c>
       <c r="E21" s="8" t="n">
-        <v>1281351.517244259</v>
+        <v>1325429.234341166</v>
       </c>
       <c r="F21" s="8" t="n">
-        <v>1346720.982409065</v>
+        <v>1461697.550610732</v>
       </c>
       <c r="G21" s="8" t="n">
         <v>1843608.3492</v>
       </c>
       <c r="H21" s="8" t="n">
-        <v>1414067.407788224</v>
+        <v>1460905.698459077</v>
       </c>
       <c r="I21" s="8" t="n">
-        <v>1483483.758223547</v>
+        <v>1588586.806455568</v>
       </c>
       <c r="J21" s="9" t="n">
-        <v>1414067</v>
+        <v>1439104</v>
       </c>
       <c r="K21" s="9" t="inlineStr">
         <is>
-          <t>Paid BF ultimate 1,414,067. Early-Green maturity (59 months, 76.4% developed). Paid CL shows elevated CDF (1.3798) with potential closure/settlement volatility. Incurred CL (1,281,352) lower; Paid CL (1,346,721) higher both with material tail extrapolation required. BF methods more credible at this maturity (exposure base stable). Paid BF selected for pragmatic development profile.</t>
+          <t>Selected 1,439,104. Green-to-early maturity (age 59 months). Weighted 35% Incurred BF (1,460,906) + 35% Incurred CL (1,325,429) + 20% Paid BF (1,588,587) + 10% Paid CL (1,461,698). BF methods are primary at this maturity; CL provides a secondary check. No prior selections.</t>
         </is>
       </c>
       <c r="L21" s="10" t="n">
-        <v>1281352</v>
+        <v>1460906</v>
       </c>
       <c r="M21" s="10" t="inlineStr">
         <is>
-          <t>Very immature (age 59). CL 1.28M selected (CDF 1.309, substantial development ahead). BF 1.41M (+435K IBNR) shows caution. IE 1.84M (+865K IBNR) may over-reserve. CL moderate, supported by BF proximity.</t>
+          <t>1,460,906 selected, following Incurred BF at 59 months (73.9% developed). Incurred CL of 1,325,429 is below both BF methods (incurred BF 1,460,906, paid BF 1,588,587), and paid CL of 1,461,698 aligns with incurred BF. At 59 months with ~74% development, BF is the most credible method. IE of 1,843,608 is above all CL/BF indications. Incurred BF at 1,460,906 is selected as a balanced estimate, consistent with paid CL and well within the range of all indications.</t>
         </is>
       </c>
       <c r="N21" s="11" t="n"/>
@@ -1521,34 +1521,34 @@
         <v>974979.4133360002</v>
       </c>
       <c r="E22" s="8" t="n">
-        <v>1389174.960078121</v>
+        <v>1436414.01140312</v>
       </c>
       <c r="F22" s="8" t="n">
-        <v>1443983.443438609</v>
+        <v>1576900.427061856</v>
       </c>
       <c r="G22" s="8" t="n">
         <v>1410360.3873</v>
       </c>
       <c r="H22" s="8" t="n">
-        <v>1394937.489175518</v>
+        <v>1428703.550087028</v>
       </c>
       <c r="I22" s="8" t="n">
-        <v>1433062.716538983</v>
+        <v>1513330.180114698</v>
       </c>
       <c r="J22" s="9" t="n">
-        <v>1394937</v>
+        <v>1469786</v>
       </c>
       <c r="K22" s="9" t="inlineStr">
         <is>
-          <t>Incurred BF ultimate 1,394,937. Green maturity (47 months, 72.8% developed). BF methods primary weight at this immaturity. Incurred BF (1,394,937) vs. Paid BF (1,433,063) show close convergence (2.7%). Incurred CL (1,389,175) also converges. Incurred BF selected for consistency with a priori assumptions and stable development. Loss ratio ~0.0030.</t>
+          <t>Selected 1,469,786. Green maturity (age 47 months). Weighted 40% Incurred BF (1,428,704) + 25% Incurred CL (1,436,414) + 20% Paid BF (1,513,330) + 15% Paid CL (1,576,900). BF is primary at this early maturity; CL is heavily discounted due to high CDFs and volatile link ratios. No prior selections.</t>
         </is>
       </c>
       <c r="L22" s="10" t="n">
-        <v>1389175</v>
+        <v>1513330</v>
       </c>
       <c r="M22" s="10" t="inlineStr">
         <is>
-          <t>Very immature (age 47). CL 1.39M selected (CDF 1.374, large tail). BF 1.39M nearly identical. IE 1.41M (+399K IBNR) similar. CL and BF strong alignment in early development stage.</t>
+          <t>1,513,330 selected, following Paid BF at 47 months (61.8% developed). At only 47 months of development, the book is approximately 60-70% developed and CL is quite leveraged. Incurred CL of 1,436,414 and paid CL of 1,576,900 bracket the BF indications (incurred BF 1,428,704, paid BF 1,513,330). IE of 1,410,360 is the a priori anchor. The paid BF of 1,513,330 best balances the credibility split at this maturity — paid losses are less subject to case reserve adequacy uncertainty, and blending with the a priori through BF is appropriate. Paid BF selected.</t>
         </is>
       </c>
       <c r="N22" s="11" t="n"/>
@@ -1568,34 +1568,34 @@
         <v>791103.7101360001</v>
       </c>
       <c r="E23" s="8" t="n">
-        <v>1332511.656834105</v>
+        <v>1369127.263774071</v>
       </c>
       <c r="F23" s="8" t="n">
-        <v>1340023.178311109</v>
+        <v>1509816.800574681</v>
       </c>
       <c r="G23" s="8" t="n">
-        <v>959045.0632000001</v>
+        <v>959045.0632</v>
       </c>
       <c r="H23" s="8" t="n">
-        <v>1190947.180739824</v>
+        <v>1206873.462196073</v>
       </c>
       <c r="I23" s="8" t="n">
-        <v>1183961.471530248</v>
+        <v>1247634.754816436</v>
       </c>
       <c r="J23" s="9" t="n">
-        <v>1332512</v>
+        <v>1301030</v>
       </c>
       <c r="K23" s="9" t="inlineStr">
         <is>
-          <t>Incurred CL ultimate 1,332,512. Very Green-Early maturity (35 months, 62.09% developed). CL entering primary weight as development accrues. Incurred CL (1,332,512) vs. Paid CL (1,340,023) show convergence (0.6%); Incurred selected for consistency. BF methods (1,190,947) show lower estimates; CL credibility higher at 62% development. Loss ratio ~0.0028.</t>
+          <t>Selected 1,301,030. Green maturity (age 35 months). Weighted 40% Incurred BF (1,206,873) + 25% Incurred CL (1,369,127) + 20% Paid BF (1,247,635) + 15% Paid CL (1,509,817). BF is primary at this early maturity; CL is heavily discounted due to high CDFs and volatile link ratios. No prior selections.</t>
         </is>
       </c>
       <c r="L23" s="10" t="n">
-        <v>1332512</v>
+        <v>1247635</v>
       </c>
       <c r="M23" s="10" t="inlineStr">
         <is>
-          <t>Very immature (age 35). CL 1.33M selected (CDF 1.610, high uncertainty). BF 1.19M shows caution (-363K vs CL). IE 0.96M appears low. CL reflects known development range; uncertainty high but CL reasonable anchor.</t>
+          <t>1,247,635 selected, following Paid BF at 35 months (52.4% developed). At 35 months, the year is just over half-developed. Incurred CL of 1,369,127 and paid CL of 1,509,817 are highly leveraged. Incurred BF of 1,206,873 and paid BF of 1,247,635 are much more stable. The IE a priori of 959,045 appears low. Paid BF at 1,247,635 is selected as a credible blend between the leveraged CL and the a priori — it uses the more stable paid development while tempering with expected losses.</t>
         </is>
       </c>
       <c r="N23" s="11" t="n"/>
@@ -1615,34 +1615,34 @@
         <v>1199242.068356001</v>
       </c>
       <c r="E24" s="8" t="n">
-        <v>3224005.220887928</v>
+        <v>3279798.511752855</v>
       </c>
       <c r="F24" s="8" t="n">
-        <v>2889398.796239016</v>
+        <v>3158470.126475578</v>
       </c>
       <c r="G24" s="8" t="n">
-        <v>978225.9646000001</v>
+        <v>978225.9645999999</v>
       </c>
       <c r="H24" s="8" t="n">
-        <v>2128807.499537224</v>
+        <v>2137333.087382769</v>
       </c>
       <c r="I24" s="8" t="n">
-        <v>1771456.328848748</v>
+        <v>1806044.627911641</v>
       </c>
       <c r="J24" s="9" t="n">
-        <v>1771456</v>
+        <v>1806125</v>
       </c>
       <c r="K24" s="9" t="inlineStr">
         <is>
-          <t>Paid BF ultimate 1,771,456. Very Green maturity (23 months, 51.23% developed). Paid CL CDF extremely elevated at 2.4094 (gross tail extrapolation risk). Incurred CL (3,224,005) shows even higher tail with CDF 1.9519 (1.57M IBNR emerging). BF methods more pragmatic: Incurred BF (2,128,807) vs. Paid BF (1,771,456). Paid BF selected for conservative positioning given excessive CL tail factors and potential case adequacy drift.</t>
+          <t>Selected 1,806,125. Very green maturity (age 23 months). Weighted 50% Incurred BF (2,137,333) + 30% Paid BF (1,806,045) + 20% Incurred IE (978,226). CL methods disqualified: Incurred CDF=1.986 and Paid CDF=2.634 are too volatile for CL reliance at 11 months. BF methods are primary; IE is secondary and shows positive IBNR (credible). No prior selections.</t>
         </is>
       </c>
       <c r="L24" s="10" t="n">
-        <v>2128807</v>
+        <v>2137333</v>
       </c>
       <c r="M24" s="10" t="inlineStr">
         <is>
-          <t>Early (age 23). CL 3.22M selected but moderated to BF 2.13M as more conservative estimate given extreme CDF 1.952 and 1.57M IBNR in CL suggests forecast noise. BF +477K IBNR more calibrated to exposure and early stage development.</t>
+          <t>2,137,333 selected, following Incurred BF at 23 months (50.4% developed). This is the most uncertain year other than 2024. Incurred CL of 3,279,799 and paid CL of 3,158,470 are extremely leveraged (CDFs of 1.99 and 2.63 respectively). The incurred BF of 2,137,333 and paid BF of 1,806,045 bracket a credible range. The incurred actual of 1,651,757 is meaningfully higher than the paid actual of 1,199,242, suggesting significant open case reserves this early. The incurred BF of 2,137,333 — which uses the incurred development pattern blended with the a priori — is preferred as it captures the case reserve signal while moderating the extreme CL leverage. IE methods (978,226) appear implausibly low given actuals already at 1.65M incurred.</t>
         </is>
       </c>
       <c r="N24" s="11" t="n"/>
@@ -1662,34 +1662,34 @@
         <v>355247.7609319999</v>
       </c>
       <c r="E25" s="8" t="n">
-        <v>2859168.092501712</v>
+        <v>2969450.702244298</v>
       </c>
       <c r="F25" s="8" t="n">
-        <v>2184729.801359199</v>
+        <v>2385840.731008563</v>
       </c>
       <c r="G25" s="8" t="n">
-        <v>997790.4837999999</v>
+        <v>997790.4838</v>
       </c>
       <c r="H25" s="8" t="n">
-        <v>1577299.9580855</v>
+        <v>1588837.049345689</v>
       </c>
       <c r="I25" s="8" t="n">
-        <v>1190792.627434757</v>
+        <v>1204468.882727955</v>
       </c>
       <c r="J25" s="9" t="n">
-        <v>1190793</v>
+        <v>1355317</v>
       </c>
       <c r="K25" s="9" t="inlineStr">
         <is>
-          <t>Paid BF ultimate 1,190,793. Extreme immaturity (11 months, 31.13% developed). Paid CL CDF 6.1499 is unmanageable without explicit tail study (extreme settlement/closure rate assumption embedded). Incurred CL shows CDF 3.212 with 1.97M IBNR (75% of current). Paid BF (1,190,793) vs. Incurred BF (1,577,300) show 33% spread. Paid BF selected as most conservative and pragmatic given massive development ahead and CL tail unreliability at extreme immaturity.</t>
+          <t>Selected 1,355,317. Very green maturity (age 11 months). Weighted 50% Incurred BF (1,588,837) + 30% Paid BF (1,204,469) + 20% Incurred IE (997,790). CL methods disqualified: Incurred CDF=3.336 and Paid CDF=6.716 are too volatile for CL reliance at 11 months. BF methods are primary; IE is secondary and shows positive IBNR (credible). No prior selections.</t>
         </is>
       </c>
       <c r="L25" s="10" t="n">
-        <v>1577300</v>
+        <v>1204469</v>
       </c>
       <c r="M25" s="10" t="inlineStr">
         <is>
-          <t>Very early (age 11). CL 2.86M with extreme CDF 3.212 reflects very incomplete development (31% developed); BF 1.58M preferred for earliest years as it moderates the volatile CDF. Actual 890K too immature to anchor; BF provides reasonable development estimate.</t>
+          <t>1,204,469 selected, following Paid BF at 11 months (14.9% developed). At 11 months the year is barely begun — paid CDF of 6.716 and incurred CDF of 3.336 are both extremely leveraged and CL indications (2,969,451 incurred, 2,385,841 paid) are unreliable. The IE a priori of 997,790 is a reasonable anchor. Incurred BF of 1,588,837 and paid BF of 1,204,469 reflect where the a priori dominates but is tempered by early actuals. Paid BF is preferred because paid losses at 11 months are the cleanest signal — incurred at this age is heavily influenced by early case reserve adequacy. Paid BF of 1,204,469 is selected as the most defensible low-maturity estimate.</t>
         </is>
       </c>
       <c r="N25" s="11" t="n"/>
@@ -1805,7 +1805,7 @@
       </c>
       <c r="H2" s="9" t="inlineStr">
         <is>
-          <t>Reported Count CL ultimate 701. Fully developed tail year (287 months, CDF 1.0). All methods (CL, IE, BF) converge at 701. No IBNR. Reported Count primary measure; CL selected as baseline method.</t>
+          <t>Selected 701. Tail maturity (age 287 months, CDF=1.00). Reported count is fully developed: CL=BF=actual=701.  IE (701) close to actual (701); consistent. No further development expected; selection equals the fully-reported count. No prior selections.</t>
         </is>
       </c>
       <c r="I2" s="10" t="n">
@@ -1813,7 +1813,7 @@
       </c>
       <c r="J2" s="10" t="inlineStr">
         <is>
-          <t>Fully mature (age 287). CL, IE, and BF all show 701.0 (CDF 1.0). Actual 701 equals ultimate; zero IBNR. Complete development.</t>
+          <t>701 selected, matching all methods (CL, IE, BF all agree). At 287 months the year is 100% developed with CDF of 1.0 and zero IBNR. The actual reported count of 701 is the ultimate.</t>
         </is>
       </c>
       <c r="K2" s="11" t="n"/>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="H3" s="9" t="inlineStr">
         <is>
-          <t>Reported Count CL ultimate 652. Fully developed (275 months, CDF 1.0). All methods converge: CL = 652, IE = 683, BF = 652. Reported Count primary; CL/BF consensus selected. Minimal IE divergence (31 counts, negligible).</t>
+          <t>Selected 652. Tail maturity (age 275 months, CDF=1.00). Reported count is fully developed: CL=BF=actual=652.  IE (683) close to actual (652); consistent. No further development expected; selection equals the fully-reported count. No prior selections.</t>
         </is>
       </c>
       <c r="I3" s="10" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="J3" s="10" t="inlineStr">
         <is>
-          <t>Mature (age 275). CL 652 selected (CDF 1.0). IE 683 (+31 IBNR), BF 652. CL reflects actual count equals ultimate; full maturity.</t>
+          <t>652 selected, matching CL and BF (both show CDF=1.0, zero IBNR). At 275 months the year is fully developed. IE of 683 reflects a slight a priori expectation above actuals, but is disregarded at this maturity. Actual count of 652 is the ultimate.</t>
         </is>
       </c>
       <c r="K3" s="11" t="n"/>
@@ -1881,7 +1881,7 @@
       </c>
       <c r="H4" s="9" t="inlineStr">
         <is>
-          <t>Reported Count CL ultimate 552. Fully developed (263 months, CDF 1.0). All methods converge: CL = 552, IE = 648, BF = 552. Reported Count primary; CL/BF consensus selected. IE shows 97-count divergence; CL/BF more credible at full maturity.</t>
+          <t>Selected 552. Tail maturity (age 263 months, CDF=1.00). Reported count is fully developed: CL=BF=actual=552.  IE (648) diverges 17% from fully-developed actual; IE not credible at this stage. No further development expected; selection equals the fully-reported count. No prior selections.</t>
         </is>
       </c>
       <c r="I4" s="10" t="n">
@@ -1889,7 +1889,7 @@
       </c>
       <c r="J4" s="10" t="inlineStr">
         <is>
-          <t>Mature (age 263). CL 552 (CDF 1.0) selected. IE 648 with +97 IBNR and BF 552. CL and BF align at actual; IE over-reserves.</t>
+          <t>552 selected, matching CL and BF (CDF=1.0, zero IBNR). At 263 months, fully developed. IE of 648 is above actuals but not credible at this maturity. Actual count of 552 is the ultimate.</t>
         </is>
       </c>
       <c r="K4" s="11" t="n"/>
@@ -1919,7 +1919,7 @@
       </c>
       <c r="H5" s="9" t="inlineStr">
         <is>
-          <t>Reported Count CL ultimate 643. Fully developed (251 months, CDF 1.0). Methods converge: CL = 643, IE = 628, BF = 643. Reported Count primary; CL/BF consensus selected. IE shows minor negative IBNR (-15); CL/BF preferred.</t>
+          <t>Selected 643. Tail maturity (age 251 months, CDF=1.00). Reported count is fully developed: CL=BF=actual=643.  IE (628) would imply negative IBNR; disqualified. No further development expected; selection equals the fully-reported count. No prior selections.</t>
         </is>
       </c>
       <c r="I5" s="10" t="n">
@@ -1927,7 +1927,7 @@
       </c>
       <c r="J5" s="10" t="inlineStr">
         <is>
-          <t>Mature (age 251). CL 643 (CDF 1.0) selected. IE 628 (-15 IBNR), BF 643. Complete development; CL at actual.</t>
+          <t>643 selected, matching CL and BF (CDF=1.0, zero IBNR). At 251 months, fully developed. IE of 628 is below actuals; disregarded at this maturity. Actual count of 643 is the ultimate.</t>
         </is>
       </c>
       <c r="K5" s="11" t="n"/>
@@ -1957,7 +1957,7 @@
       </c>
       <c r="H6" s="9" t="inlineStr">
         <is>
-          <t>Reported Count CL ultimate 641. Fully developed (239 months, CDF 1.0). Methods converge: CL = 641, IE = 624, BF = 641. Reported Count primary; CL/BF consensus selected. IE shows negative IBNR (-18); CL/BF credible.</t>
+          <t>Selected 641. Tail maturity (age 239 months, CDF=1.00). Reported count is fully developed: CL=BF=actual=641.  IE (624) would imply negative IBNR; disqualified. No further development expected; selection equals the fully-reported count. No prior selections.</t>
         </is>
       </c>
       <c r="I6" s="10" t="n">
@@ -1965,7 +1965,7 @@
       </c>
       <c r="J6" s="10" t="inlineStr">
         <is>
-          <t>Mature (age 239). CL 641 (CDF 1.0) selected. IE 624 (-18 IBNR), BF 641. Full maturity; CL-BF perfect alignment at actual.</t>
+          <t>641 selected, matching CL and BF (CDF=1.0, zero IBNR). At 239 months, fully developed. IE of 624 is slightly below actuals; disregarded. Actual count of 641 is the ultimate.</t>
         </is>
       </c>
       <c r="K6" s="11" t="n"/>
@@ -1995,7 +1995,7 @@
       </c>
       <c r="H7" s="9" t="inlineStr">
         <is>
-          <t>Reported Count CL ultimate 497. Fully developed (227 months, CDF 1.0). Methods converge: CL = 497, IE = 607, BF = 497. Reported Count primary; CL/BF consensus selected. IE shows 110-count divergence indicating a priori mismatch.</t>
+          <t>Selected 497. Tail maturity (age 227 months, CDF=1.00). Reported count is fully developed: CL=BF=actual=497.  IE (607) diverges 22% from fully-developed actual; IE not credible at this stage. No further development expected; selection equals the fully-reported count. No prior selections.</t>
         </is>
       </c>
       <c r="I7" s="10" t="n">
@@ -2003,7 +2003,7 @@
       </c>
       <c r="J7" s="10" t="inlineStr">
         <is>
-          <t>Mature (age 227). CL 497 (CDF 1.0) selected. IE 607 (+109 IBNR), BF 497. Complete development; CL matches actual.</t>
+          <t>497 selected, matching CL and BF (CDF=1.0, zero IBNR). At 227 months, fully developed. IE of 607 is above actuals but disregarded at this maturity. Actual count of 497 is the ultimate.</t>
         </is>
       </c>
       <c r="K7" s="11" t="n"/>
@@ -2033,7 +2033,7 @@
       </c>
       <c r="H8" s="9" t="inlineStr">
         <is>
-          <t>Reported Count CL ultimate 476. Fully developed (215 months, CDF 1.0). Methods converge: CL = 476, IE = 550, BF = 476. Reported Count primary; CL/BF consensus selected. IE shows 74-count divergence; CL/BF more credible.</t>
+          <t>Selected 476. Tail maturity (age 215 months, CDF=1.00). Reported count is fully developed: CL=BF=actual=476.  IE (550) diverges 16% from fully-developed actual; IE not credible at this stage. No further development expected; selection equals the fully-reported count. No prior selections.</t>
         </is>
       </c>
       <c r="I8" s="10" t="n">
@@ -2041,7 +2041,7 @@
       </c>
       <c r="J8" s="10" t="inlineStr">
         <is>
-          <t>Mature (age 215). CL 476 (CDF 1.0) selected. IE 550 (+74 IBNR), BF 476. Full maturity; CL at actual.</t>
+          <t>476 selected, matching CL and BF (CDF=1.0, zero IBNR). At 215 months, fully developed. IE of 550 is above actuals; disregarded. Actual count of 476 is the ultimate.</t>
         </is>
       </c>
       <c r="K8" s="11" t="n"/>
@@ -2061,7 +2061,7 @@
         <v>328.5804000000001</v>
       </c>
       <c r="E9" s="8" t="n">
-        <v>444.0969799109999</v>
+        <v>444.096979911</v>
       </c>
       <c r="F9" s="8" t="n">
         <v>328.5804000000001</v>
@@ -2071,7 +2071,7 @@
       </c>
       <c r="H9" s="9" t="inlineStr">
         <is>
-          <t>Reported Count CL ultimate 329. Fully developed (203 months, CDF 1.0). Methods converge: CL = 329, IE = 444, BF = 329. Reported Count primary; CL/BF consensus selected. IE shows significant divergence (116 counts); CL/BF preferred.</t>
+          <t>Selected 329. Tail maturity (age 203 months, CDF=1.00). Reported count is fully developed: CL=BF=actual=329.  IE (444) diverges 35% from fully-developed actual; IE not credible at this stage. No further development expected; selection equals the fully-reported count. No prior selections.</t>
         </is>
       </c>
       <c r="I9" s="10" t="n">
@@ -2079,7 +2079,7 @@
       </c>
       <c r="J9" s="10" t="inlineStr">
         <is>
-          <t>Mature (age 203). CL 329 (CDF 1.0) selected. IE 444 (+116 IBNR), BF 329. Complete development; CL conservative.</t>
+          <t>329 selected, matching CL and BF (CDF=1.0, zero IBNR). At 203 months, fully developed. IE of 444 is materially above actuals, reflecting the substantial drop in claim counts from prior years; disregarded at this maturity. Actual count of 329 is the ultimate.</t>
         </is>
       </c>
       <c r="K9" s="11" t="n"/>
@@ -2109,7 +2109,7 @@
       </c>
       <c r="H10" s="9" t="inlineStr">
         <is>
-          <t>Reported Count CL ultimate 322. Fully developed (191 months, CDF 1.0). Methods converge: CL = 322, IE = 384, BF = 322. Reported Count primary; CL/BF consensus selected. IE shows 62-count divergence; CL/BF credible.</t>
+          <t>Selected 322. Tail maturity (age 191 months, CDF=1.00). Reported count is fully developed: CL=BF=actual=322.  IE (384) diverges 19% from fully-developed actual; IE not credible at this stage. No further development expected; selection equals the fully-reported count. No prior selections.</t>
         </is>
       </c>
       <c r="I10" s="10" t="n">
@@ -2117,7 +2117,7 @@
       </c>
       <c r="J10" s="10" t="inlineStr">
         <is>
-          <t>Mature (age 191). CL 322 (CDF 1.0) selected. IE 384 (+62 IBNR), BF 322. Full development; CL-BF agreement.</t>
+          <t>322 selected, matching CL and BF (CDF=1.0, zero IBNR). At 191 months, fully developed. IE of 384 is above actuals; disregarded. Actual count of 322 is the ultimate.</t>
         </is>
       </c>
       <c r="K10" s="11" t="n"/>
@@ -2147,7 +2147,7 @@
       </c>
       <c r="H11" s="9" t="inlineStr">
         <is>
-          <t>Reported Count CL ultimate 272. Fully developed (179 months, CDF 1.0). Methods converge: CL = 272, IE = 314, BF = 272. Reported Count primary; CL/BF consensus selected. IE shows 42-count divergence; CL/BF more credible.</t>
+          <t>Selected 272. Tail maturity (age 179 months, CDF=1.00). Reported count is fully developed: CL=BF=actual=272.  IE (314) diverges 15% from fully-developed actual; IE not credible at this stage. No further development expected; selection equals the fully-reported count. No prior selections.</t>
         </is>
       </c>
       <c r="I11" s="10" t="n">
@@ -2155,7 +2155,7 @@
       </c>
       <c r="J11" s="10" t="inlineStr">
         <is>
-          <t>Mature (age 179). CL 272 (CDF 1.0) selected. IE 314 (+42 IBNR), BF 272. Complete development; CL at actual.</t>
+          <t>272 selected, matching CL and BF (CDF=1.0, zero IBNR). At 179 months, fully developed. IE of 314 is above actuals; disregarded. Actual count of 272 is the ultimate.</t>
         </is>
       </c>
       <c r="K11" s="11" t="n"/>
@@ -2185,7 +2185,7 @@
       </c>
       <c r="H12" s="9" t="inlineStr">
         <is>
-          <t>Reported Count CL ultimate 346. Fully developed (167 months, CDF 1.0). Methods converge: CL = 346, IE = 319, BF = 346. Reported Count primary; CL/BF consensus selected. IE shows negative IBNR (-26); CL/BF preferred.</t>
+          <t>Selected 346. Tail maturity (age 167 months, CDF=1.00). Reported count is fully developed: CL=BF=actual=346.  IE (319) would imply negative IBNR; disqualified. No further development expected; selection equals the fully-reported count. No prior selections.</t>
         </is>
       </c>
       <c r="I12" s="10" t="n">
@@ -2193,7 +2193,7 @@
       </c>
       <c r="J12" s="10" t="inlineStr">
         <is>
-          <t>Mature (age 167). CL 346 (CDF 1.0) selected. IE 319 (-26 IBNR), BF 346. Full maturity; CL matches actual.</t>
+          <t>346 selected, matching CL and BF (CDF=1.0, zero IBNR). At 167 months, fully developed. IE of 319 is below actuals; disregarded at this maturity. Actual count of 346 is the ultimate.</t>
         </is>
       </c>
       <c r="K12" s="11" t="n"/>
@@ -2223,7 +2223,7 @@
       </c>
       <c r="H13" s="9" t="inlineStr">
         <is>
-          <t>Reported Count CL ultimate 261. Fully developed (155 months, CDF 1.0). Methods converge: CL = 261, IE = 299, BF = 261. Reported Count primary; CL/BF consensus selected. IE shows 38-count divergence; CL/BF credible.</t>
+          <t>Selected 261. Tail maturity (age 155 months, CDF=1.00). Reported count is fully developed: CL=BF=actual=261.  IE (299) close to actual (261); consistent. No further development expected; selection equals the fully-reported count. No prior selections.</t>
         </is>
       </c>
       <c r="I13" s="10" t="n">
@@ -2231,7 +2231,7 @@
       </c>
       <c r="J13" s="10" t="inlineStr">
         <is>
-          <t>Mature (age 155). CL 261 (CDF 1.0) selected. IE 299 (+38 IBNR), BF 261. Complete development; CL conservative.</t>
+          <t>261 selected, matching CL and BF (CDF=1.0, zero IBNR). At 155 months, fully developed. IE of 299 is above actuals; disregarded. Actual count of 261 is the ultimate.</t>
         </is>
       </c>
       <c r="K13" s="11" t="n"/>
@@ -2261,7 +2261,7 @@
       </c>
       <c r="H14" s="9" t="inlineStr">
         <is>
-          <t>Reported Count CL ultimate 292. Fully developed (143 months, CDF 1.0). Methods converge: CL = 292, IE = 306, BF = 292. Reported Count primary; CL/BF consensus selected. IE shows 14-count divergence (minimal); CL/BF preferred.</t>
+          <t>Selected 292. Tail maturity (age 143 months, CDF=1.00). Reported count is fully developed: CL=BF=actual=292.  IE (306) close to actual (292); consistent. No further development expected; selection equals the fully-reported count. No prior selections.</t>
         </is>
       </c>
       <c r="I14" s="10" t="n">
@@ -2269,7 +2269,7 @@
       </c>
       <c r="J14" s="10" t="inlineStr">
         <is>
-          <t>Mature (age 143). CL 292 (CDF 1.0) selected. IE 306 (+14 IBNR), BF 292. Full development; CL-BF align.</t>
+          <t>292 selected, matching CL and BF (CDF=1.0, zero IBNR). At 143 months, fully developed. IE of 306 is close to actuals but both CL and BF agree with the actual. Actual count of 292 is the ultimate.</t>
         </is>
       </c>
       <c r="K14" s="11" t="n"/>
@@ -2299,7 +2299,7 @@
       </c>
       <c r="H15" s="9" t="inlineStr">
         <is>
-          <t>Reported Count CL ultimate 455. Fully developed (131 months, CDF 1.0). Methods converge: CL = 455, IE = 341, BF = 455. Reported Count primary; CL/BF consensus selected. IE shows negative IBNR (-114); CL/BF more credible.</t>
+          <t>Selected 455. Tail maturity (age 131 months, CDF=1.00). Reported count is fully developed: CL=BF=actual=455.  IE (341) diverges 25% from fully-developed actual; IE not credible at this stage. No further development expected; selection equals the fully-reported count. No prior selections.</t>
         </is>
       </c>
       <c r="I15" s="10" t="n">
@@ -2307,7 +2307,7 @@
       </c>
       <c r="J15" s="10" t="inlineStr">
         <is>
-          <t>Mature (age 131). CL 455 (CDF 1.0) selected. IE 341 (-114 IBNR), BF 455. Complete development; CL at actual.</t>
+          <t>455 selected, matching CL and BF (CDF=1.0, zero IBNR). At 131 months, fully developed. IE of 341 is well below actuals — this is a high-count year relative to the a priori. Both CL and BF agree at 455. Actual count of 455 is the ultimate.</t>
         </is>
       </c>
       <c r="K15" s="11" t="n"/>
@@ -2337,7 +2337,7 @@
       </c>
       <c r="H16" s="9" t="inlineStr">
         <is>
-          <t>Reported Count CL ultimate 334. Fully developed (119 months, CDF 1.0). Methods converge: CL = 334, IE = 367, BF = 334. Reported Count primary; CL/BF consensus selected. IE shows 34-count divergence; CL/BF preferred.</t>
+          <t>Selected 334. Tail maturity (age 119 months, CDF=1.00). Reported count is fully developed: CL=BF=actual=334.  IE (367) close to actual (334); consistent. No further development expected; selection equals the fully-reported count. No prior selections.</t>
         </is>
       </c>
       <c r="I16" s="10" t="n">
@@ -2345,7 +2345,7 @@
       </c>
       <c r="J16" s="10" t="inlineStr">
         <is>
-          <t>Mature (age 119). CL 334 (CDF 1.0) selected. IE 367 (+34 IBNR), BF 334. Full maturity; CL matches actual.</t>
+          <t>334 selected, matching CL and BF (CDF=1.0, zero IBNR). At 119 months, fully developed. IE of 367 is modestly above actuals; disregarded. Actual count of 334 is the ultimate.</t>
         </is>
       </c>
       <c r="K16" s="11" t="n"/>
@@ -2375,7 +2375,7 @@
       </c>
       <c r="H17" s="9" t="inlineStr">
         <is>
-          <t>Reported Count CL ultimate 391. Fully developed (107 months, CDF 1.0). Methods converge: CL = 391, IE = 402, BF = 391. Reported Count primary; CL/BF consensus selected. IE shows 11-count divergence (minimal); CL/BF credible.</t>
+          <t>Selected 391. Tail maturity (age 107 months, CDF=1.00). Reported count is fully developed: CL=BF=actual=391.  IE (402) close to actual (391); consistent. No further development expected; selection equals the fully-reported count. No prior selections.</t>
         </is>
       </c>
       <c r="I17" s="10" t="n">
@@ -2383,7 +2383,7 @@
       </c>
       <c r="J17" s="10" t="inlineStr">
         <is>
-          <t>Mature (age 107). CL 391 (CDF 1.0) selected. IE 402 (+11 IBNR), BF 391. Complete development; CL-BF perfect agreement.</t>
+          <t>391 selected, matching CL and BF (CDF=1.0, zero IBNR). At 107 months, fully developed. IE of 402 is close but both CL and BF confirm full development. Actual count of 391 is the ultimate.</t>
         </is>
       </c>
       <c r="K17" s="11" t="n"/>
@@ -2413,7 +2413,7 @@
       </c>
       <c r="H18" s="9" t="inlineStr">
         <is>
-          <t>Reported Count CL ultimate 310. Fully developed (95 months, CDF 1.0). Methods converge: CL = 310, IE = 352, BF = 310. Reported Count primary; CL/BF consensus selected. IE shows 42-count divergence; CL/BF preferred.</t>
+          <t>Selected 310. Tail maturity (age 95 months, CDF=1.00). Reported count is fully developed: CL=BF=actual=310.  IE (352) close to actual (310); consistent. No further development expected; selection equals the fully-reported count. No prior selections.</t>
         </is>
       </c>
       <c r="I18" s="10" t="n">
@@ -2421,7 +2421,7 @@
       </c>
       <c r="J18" s="10" t="inlineStr">
         <is>
-          <t>Mature (age 95). CL 310 (CDF 1.0) selected. IE 352 (+42 IBNR), BF 310. Full development; CL conservative at actual.</t>
+          <t>310 selected, matching CL and BF (CDF=1.0, zero IBNR). At 95 months, fully developed. IE of 352 is above actuals; disregarded. Actual count of 310 is the ultimate.</t>
         </is>
       </c>
       <c r="K18" s="11" t="n"/>
@@ -2451,7 +2451,7 @@
       </c>
       <c r="H19" s="9" t="inlineStr">
         <is>
-          <t>Reported Count CL ultimate 326. Fully developed (83 months, CDF 1.0). Methods converge: CL = 326, IE = 350, BF = 326. Reported Count primary; CL/BF consensus selected. IE shows 24-count divergence; CL/BF credible.</t>
+          <t>Selected 326. Late maturity (age 83 months, CDF=1.00). Reported count is fully developed: CL=BF=actual=326.  IE (350) close to actual (326); consistent. No further development expected; selection equals the fully-reported count. No prior selections.</t>
         </is>
       </c>
       <c r="I19" s="10" t="n">
@@ -2459,7 +2459,7 @@
       </c>
       <c r="J19" s="10" t="inlineStr">
         <is>
-          <t>Mature (age 83). CL 326 (CDF 1.0) selected. IE 350 (+24 IBNR), BF 326. Complete development; CL matches actual.</t>
+          <t>326 selected, matching CL and BF (CDF=1.0, zero IBNR). At 83 months, fully developed. IE of 350 is modestly above actuals. Both CL and BF confirm full development. Actual count of 326 is the ultimate.</t>
         </is>
       </c>
       <c r="K19" s="11" t="n"/>
@@ -2489,7 +2489,7 @@
       </c>
       <c r="H20" s="9" t="inlineStr">
         <is>
-          <t>Reported Count CL ultimate 358. Fully developed (71 months, CDF 1.0). Methods converge: CL = 358, IE = 338, BF = 358. Reported Count primary; CL/BF consensus selected. IE shows negative IBNR (-20); CL/BF preferred.</t>
+          <t>Selected 358. Late maturity (age 71 months, CDF=1.00). Reported count is fully developed: CL=BF=actual=358.  IE (338) would imply negative IBNR; disqualified. No further development expected; selection equals the fully-reported count. No prior selections.</t>
         </is>
       </c>
       <c r="I20" s="10" t="n">
@@ -2497,7 +2497,7 @@
       </c>
       <c r="J20" s="10" t="inlineStr">
         <is>
-          <t>Mature (age 71). CL 358 (CDF 1.0) selected. IE 338 (-20 IBNR), BF 358. Full development; CL at actual.</t>
+          <t>358 selected, matching CL and BF (CDF=1.0, zero IBNR). At 71 months, fully developed. IE of 338 is slightly below actuals. CL and BF agree at 358. Actual count of 358 is the ultimate.</t>
         </is>
       </c>
       <c r="K20" s="11" t="n"/>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="H21" s="9" t="inlineStr">
         <is>
-          <t>Reported Count CL ultimate 371. Fully developed (59 months, CDF 1.0). Methods converge: CL = 371, IE = 358, BF = 371. Reported Count primary; CL/BF consensus selected. IE shows negative IBNR (-13); CL/BF credible.</t>
+          <t>Selected 371. Mid maturity (age 59 months, CDF=1.00). Reported count is fully developed: CL=BF=actual=371.  IE (358) would imply negative IBNR; disqualified. No further development expected; selection equals the fully-reported count. No prior selections.</t>
         </is>
       </c>
       <c r="I21" s="10" t="n">
@@ -2535,7 +2535,7 @@
       </c>
       <c r="J21" s="10" t="inlineStr">
         <is>
-          <t>Mature (age 59). CL 371 (CDF 1.0) selected. IE 358 (-13 IBNR), BF 371. Complete development; CL-BF agreement.</t>
+          <t>371 selected, matching CL and BF (CDF=1.0, zero IBNR). At 59 months, fully developed per CL. IE of 358 is close but CL and BF both confirm no remaining development. Actual count of 371 is the ultimate.</t>
         </is>
       </c>
       <c r="K21" s="11" t="n"/>
@@ -2565,7 +2565,7 @@
       </c>
       <c r="H22" s="9" t="inlineStr">
         <is>
-          <t>Reported Count CL ultimate 330. Fully developed (47 months, CDF 1.0). Methods converge: CL = 330, IE = 360, BF = 330. Reported Count primary; CL/BF consensus selected. IE shows 30-count divergence; CL/BF preferred.</t>
+          <t>Selected 330. Mid maturity (age 47 months, CDF=1.00). Reported count is fully developed: CL=BF=actual=330.  IE (360) close to actual (330); consistent. No further development expected; selection equals the fully-reported count. No prior selections.</t>
         </is>
       </c>
       <c r="I22" s="10" t="n">
@@ -2573,7 +2573,7 @@
       </c>
       <c r="J22" s="10" t="inlineStr">
         <is>
-          <t>Mature (age 47). CL 330 (CDF 1.0) selected. IE 360 (+30 IBNR), BF 330. Full development; CL matches actual.</t>
+          <t>330 selected, matching CL and BF (CDF=1.0, zero IBNR). At 47 months, CL and BF both show full development with zero IBNR. IE of 360 is modestly above actuals. Actual count of 330 is the ultimate.</t>
         </is>
       </c>
       <c r="K22" s="11" t="n"/>
@@ -2590,20 +2590,20 @@
         <v>298.2296</v>
       </c>
       <c r="D23" s="8" t="n">
-        <v>298.34889184</v>
+        <v>298.2296</v>
       </c>
       <c r="E23" s="8" t="n">
         <v>339.9814749044</v>
       </c>
       <c r="F23" s="8" t="n">
-        <v>298.3655382146759</v>
+        <v>298.2296</v>
       </c>
       <c r="G23" s="9" t="n">
         <v>298</v>
       </c>
       <c r="H23" s="9" t="inlineStr">
         <is>
-          <t>Reported Count CL ultimate 298. Nearly fully developed (35 months, CDF 1.0004, 99.96%). Methods converge: CL = 298, IE = 340, BF = 298. Reported Count primary; CL/BF consensus selected. IE shows 42-count divergence indicating a priori mismatch. CL credible at near-full development.</t>
+          <t>Selected 298. Early-mid maturity (age 35 months, CDF=1.00). Reported count is fully developed: CL=BF=actual=298.  IE (340) close to actual (298); consistent. No further development expected; selection equals the fully-reported count. No prior selections.</t>
         </is>
       </c>
       <c r="I23" s="10" t="n">
@@ -2611,7 +2611,7 @@
       </c>
       <c r="J23" s="10" t="inlineStr">
         <is>
-          <t>Near-mature (age 35). CL 298 selected (CDF 1.0004, essentially mature). IE 340 (+42 IBNR), BF 298. Virtually complete development; CL-BF align.</t>
+          <t>298 selected, matching CL and BF (CDF=1.0, zero IBNR). At 35 months, CL and BF both show full development with zero IBNR — an unusual finding for a relatively young year, but the data shows no remaining development pattern. IE of 340 is above actuals. Actual count of 298 is the ultimate.</t>
         </is>
       </c>
       <c r="K23" s="11" t="n"/>
@@ -2628,20 +2628,20 @@
         <v>304.8276</v>
       </c>
       <c r="D24" s="8" t="n">
-        <v>304.94953104</v>
+        <v>305.4372552</v>
       </c>
       <c r="E24" s="8" t="n">
         <v>317.4343255127</v>
       </c>
       <c r="F24" s="8" t="n">
-        <v>304.9545229610207</v>
+        <v>305.4612014481292</v>
       </c>
       <c r="G24" s="9" t="n">
         <v>305</v>
       </c>
       <c r="H24" s="9" t="inlineStr">
         <is>
-          <t>Reported Count CL ultimate 305. Nearly fully developed (23 months, CDF 1.0004, 99.96%). Methods converge: CL = 305, IE = 317, BF = 305. Reported Count primary; CL/BF consensus selected. IE shows 13-count divergence (minimal). CL/BF convergence indicates credibility. No material IBNR.</t>
+          <t>Selected 305. Green maturity (age 23 months, CDF=1.002). BF (305) and CL (305) converge within 0.0% — BF selected as primary method appropriate for this maturity. IE (317) is 3.9% above BF; IE provides secondary confirmation of slightly higher development but BF is preferred. No prior selections.</t>
         </is>
       </c>
       <c r="I24" s="10" t="n">
@@ -2649,7 +2649,7 @@
       </c>
       <c r="J24" s="10" t="inlineStr">
         <is>
-          <t>Near-mature (age 23). CL 305 selected (CDF 1.0004, essentially mature). IE 317 (+13 IBNR), BF 305. Near-complete development; CL at actual.</t>
+          <t>305 selected, following CL and BF (both indicate 305, with CDF of 1.002 leaving only 1 claim of IBNR). At 23 months, there is minimal residual development remaining per the triangle. IE of 317 adds only modest signal. CL and BF agree tightly; BF of 305 is selected as it blends the a priori while the residual development is negligible. The CL and BF are nearly identical at this near-fully-developed point for counts.</t>
         </is>
       </c>
       <c r="K24" s="11" t="n"/>
@@ -2666,28 +2666,28 @@
         <v>256.0024</v>
       </c>
       <c r="D25" s="8" t="n">
-        <v>290.16673948768</v>
+        <v>279.6007012320001</v>
       </c>
       <c r="E25" s="8" t="n">
         <v>292.3526117534</v>
       </c>
       <c r="F25" s="8" t="n">
-        <v>290.4241048986661</v>
+        <v>280.6769625734114</v>
       </c>
       <c r="G25" s="9" t="n">
-        <v>290</v>
+        <v>281</v>
       </c>
       <c r="H25" s="9" t="inlineStr">
         <is>
-          <t>Reported Count CL ultimate 290. Early maturity (11 months, CDF 1.1335, 88.23% developed). Methods show tight convergence: CL = 290, IE = 292, BF = 290. Reported Count primary; convergence check applied: CL/BF consensus at 290 selected over IE at 292. 1% divergence within reasonable bounds at this immaturity. 34 counts IBNR expected.</t>
+          <t>Selected 281. Green maturity (age 11 months, CDF=1.092). BF (281) and CL (280) converge within 0.4% — BF selected as primary method appropriate for this maturity. IE (292) is 3.9% above BF; IE provides secondary confirmation of slightly higher development but BF is preferred. No prior selections.</t>
         </is>
       </c>
       <c r="I25" s="10" t="n">
-        <v>290</v>
+        <v>281</v>
       </c>
       <c r="J25" s="10" t="inlineStr">
         <is>
-          <t>Immature (age 11). CL 290 selected (CDF 1.134, modest expected development). IE 292 (+36 IBNR), BF 290. Early stage; CL and BF aligned (+34 IBNR). Expect ~34 additional counts before full maturity.</t>
+          <t>281 selected, following BF at 11 months (91.6% developed). CDF of 1.0922 indicates roughly 8% of counts remain unreported. CL indicates 280, BF indicates 281, and IE indicates 292 — all three methods are tightly clustered. BF of 281 is selected as it appropriately blends the actual 256 reported counts with a priori expectations for the residual development. The IE at 292 provides a modest upward check. The tight convergence of all three methods provides comfort in the selection.</t>
         </is>
       </c>
       <c r="K25" s="11" t="n"/>

--- a/sample-data/sample-run/selections/Ultimates.xlsx
+++ b/sample-data/sample-run/selections/Ultimates.xlsx
@@ -538,12 +538,12 @@
       </c>
       <c r="J1" s="2" t="inlineStr">
         <is>
-          <t>Rules-Based AI Selection</t>
+          <t>Framework AI Selection</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>Rules-Based AI Reasoning</t>
+          <t>Framework AI Reasoning</t>
         </is>
       </c>
       <c r="L1" s="2" t="inlineStr">
@@ -600,7 +600,7 @@
       </c>
       <c r="K2" s="9" t="inlineStr">
         <is>
-          <t>Selected 3,163,774. Tail maturity (age 287 months, CDF=1.00). Period is fully developed per both incurred and paid CDFs. Incurred CL equals the actual incurred value with zero IBNR, representing a fully closed book. Paid CL is slightly lower (3,042,295), consistent with some remaining case reserves on open claims. Incurred CL preferred as the more complete measure. IE and BF are irrelevant at 100% development. No prior selections available.</t>
+          <t>Selected Incurred Chain Ladder ultimate of $3,163,774. At age 287mo (Tail bucket), the CDF is 1.000 (pct developed 100%), so the incurred triangle is fully mature and BF/IE are not additive. Paid CL ($3,042,295, 4.0% below) reflects the small remaining case reserve on open claims yet to be disbursed; Incurred CL is preferred as the more complete final-cost estimate. Implied loss ratio ~1.00% of exposure, consistent with this line's large-claim volatility given low claim counts (701 reported).</t>
         </is>
       </c>
       <c r="L2" s="10" t="n">
@@ -608,7 +608,7 @@
       </c>
       <c r="M2" s="10" t="inlineStr">
         <is>
-          <t>3,163,774 selected, matching Incurred CL (and IE/BF, all identical). At 287 months the year is fully developed; all methods agree and no IBNR remains. Paid CL of 3,042,295 is slightly lower but incurred is appropriate given full maturity. Zero uncertainty remains.</t>
+          <t>Selected $3,163,774 from Incurred Chain Ladder (= actual, CDF 1.00). At 287 months maturity this AY is fully developed on both measures (paid actual of $3.04M is only ~4% lower, reflecting a small residual case reserve on an otherwise closed year); incurred is used as the more complete measure of ultimate liability including that residual reserve. No further judgment adjustment needed at this maturity.</t>
         </is>
       </c>
       <c r="N2" s="11" t="n"/>
@@ -628,34 +628,34 @@
         <v>2199646.228088</v>
       </c>
       <c r="E3" s="8" t="n">
-        <v>2334716.957588959</v>
+        <v>2327733.756319999</v>
       </c>
       <c r="F3" s="8" t="n">
-        <v>2210644.45922844</v>
+        <v>2230441.275281232</v>
       </c>
       <c r="G3" s="8" t="n">
         <v>2904344.256599999</v>
       </c>
       <c r="H3" s="8" t="n">
-        <v>2336420.728174236</v>
+        <v>2327733.756319999</v>
       </c>
       <c r="I3" s="8" t="n">
-        <v>2214095.702001432</v>
+        <v>2239745.655693917</v>
       </c>
       <c r="J3" s="9" t="n">
-        <v>2297495</v>
+        <v>2327734</v>
       </c>
       <c r="K3" s="9" t="inlineStr">
         <is>
-          <t>Selected 2,297,495. Tail maturity (age 275 months). Weighted 70% Incurred CL (2,334,717) + 30% Paid CL (2,210,644). IE disqualified (highly divergent from CL with implausible IBNR). BF near-identical to CL at this maturity. No prior selections.</t>
+          <t>Selected Incurred Chain Ladder ultimate of $2,327,734, fully developed (CDF 1.000). Paid CL is close (-4.2%); IE ($2,904,344) is stale/uninformative at full maturity and is disregarded (BF assumptions not applicable once pct developed = 100%). No prior selection to anchor to.</t>
         </is>
       </c>
       <c r="L3" s="10" t="n">
-        <v>2334717</v>
+        <v>2327734</v>
       </c>
       <c r="M3" s="10" t="inlineStr">
         <is>
-          <t>2,334,717 selected, following Incurred CL at 275 months maturity (99.7% developed). CDF of 1.003 applies only a trivial tail. Paid CL of 2,210,644 is notably lower than incurred, suggesting some open reserves remain; incurred CL is the more reliable signal at this maturity. IE of 2,904,344 is implausibly high relative to actuals and not credible here.</t>
+          <t>Selected $2,327,734 from Incurred Chain Ladder (= actual, CDF 1.00). Fully developed; paid is close ($2.20M actual, $2.23M CL ultimate) confirming convergence. Incurred CL is the most credible indication at this maturity; the Initial Expected ($2.90M) is a stale a priori that overstates this year's experience and is disregarded.</t>
         </is>
       </c>
       <c r="N3" s="11" t="n"/>
@@ -675,34 +675,34 @@
         <v>1778091.575843999</v>
       </c>
       <c r="E4" s="8" t="n">
-        <v>1788776.128123245</v>
+        <v>1778091.575843999</v>
       </c>
       <c r="F4" s="8" t="n">
-        <v>1795916.943891835</v>
+        <v>1815605.751911156</v>
       </c>
       <c r="G4" s="8" t="n">
         <v>2633272.1256</v>
       </c>
       <c r="H4" s="8" t="n">
-        <v>1793820.393580948</v>
+        <v>1778091.575843999</v>
       </c>
       <c r="I4" s="8" t="n">
-        <v>1804228.110146753</v>
+        <v>1832500.433079944</v>
       </c>
       <c r="J4" s="9" t="n">
-        <v>1792346</v>
+        <v>1778092</v>
       </c>
       <c r="K4" s="9" t="inlineStr">
         <is>
-          <t>Selected 1,792,346. Tail maturity (age 263 months). Incurred CL (1,788,776) and Paid CL (1,795,917) converge within 0.4% — convergence rule applied, selecting midpoint. BF near-identical to CL at this maturity. No prior selections.</t>
+          <t>Selected Incurred Chain Ladder ultimate of $1,778,092, fully developed (CDF 1.000, actual = ultimate). Paid CL is 2.1% higher, a minor and immaterial divergence confirming the estimate. Tail bucket: CL primary, BF/IE not weighted at full maturity.</t>
         </is>
       </c>
       <c r="L4" s="10" t="n">
-        <v>1795917</v>
+        <v>1778092</v>
       </c>
       <c r="M4" s="10" t="inlineStr">
         <is>
-          <t>1,795,917 selected, following Paid CL at 263 months (99.0% developed). Incurred CL is 1,788,776 — essentially identical to paid (actual incurred and paid are both 1,778,092, implying reserves are near zero). Paid CL is preferred as it confirms no open case reserves inflating incurred. IE of 2,633,272 is far above actuals and lacks credibility at this maturity.</t>
+          <t>Selected $1,778,092 from Incurred Chain Ladder (= actual, CDF 1.00). Incurred and paid actuals are identical at this age, indicating the year is essentially fully settled with no open case reserve. Highest-credibility, fully-developed indication; IE ($2.63M) is not reflective of actual experience and is given no weight.</t>
         </is>
       </c>
       <c r="N4" s="11" t="n"/>
@@ -722,34 +722,34 @@
         <v>1122614.7306</v>
       </c>
       <c r="E5" s="8" t="n">
-        <v>1132748.604083724</v>
+        <v>1138331.3368284</v>
       </c>
       <c r="F5" s="8" t="n">
-        <v>1139538.287990636</v>
+        <v>1153177.454123316</v>
       </c>
       <c r="G5" s="8" t="n">
         <v>1678710.98</v>
       </c>
       <c r="H5" s="8" t="n">
-        <v>1137632.930247943</v>
+        <v>1145792.199751874</v>
       </c>
       <c r="I5" s="8" t="n">
-        <v>1147545.671413245</v>
+        <v>1167105.697167066</v>
       </c>
       <c r="J5" s="9" t="n">
-        <v>1136144</v>
+        <v>1138331</v>
       </c>
       <c r="K5" s="9" t="inlineStr">
         <is>
-          <t>Selected 1,136,144. Tail maturity (age 251 months). Incurred CL (1,132,749) and Paid CL (1,139,538) converge within 0.6% — convergence rule applied, selecting midpoint. BF near-identical to CL at this maturity. No prior selections.</t>
+          <t>Selected Incurred Chain Ladder ultimate of $1,138,331 (pct developed 98.6%, Tail bucket). Paid CL ($1,153,177) is within 1.3% -- a convergence signal supporting the CL selection over BF ($1,145,792, close) and the clearly stale IE ($1,678,711, disregarded as BF/IE lose informativeness at this maturity).</t>
         </is>
       </c>
       <c r="L5" s="10" t="n">
-        <v>1132749</v>
+        <v>1138331</v>
       </c>
       <c r="M5" s="10" t="inlineStr">
         <is>
-          <t>1,132,749 selected, following Incurred CL at 251 months (99.1% developed). Incurred and Paid CL are nearly identical (1,132,749 vs 1,139,538) confirming stability. Actuals are the same for both measures indicating minimal open reserves. IE of 1,678,711 is far above actuals at near-full maturity and is disregarded.</t>
+          <t>Selected $1,138,331 from Incurred Chain Ladder (CDF 1.014, minor 1.4% tail). Incurred and paid actuals are identical at this age (year effectively closed), so CL's small residual development is applied as a modest prudent margin for late reopenings. IE ($1.68M) is far off actual experience and not credible for this small, well-developed year.</t>
         </is>
       </c>
       <c r="N5" s="11" t="n"/>
@@ -769,34 +769,34 @@
         <v>2242149.132116</v>
       </c>
       <c r="E6" s="8" t="n">
-        <v>2269176.240088246</v>
+        <v>2282633.376845487</v>
       </c>
       <c r="F6" s="8" t="n">
-        <v>2287329.559604046</v>
+        <v>2314706.672064777</v>
       </c>
       <c r="G6" s="8" t="n">
         <v>1712285.2</v>
       </c>
       <c r="H6" s="8" t="n">
-        <v>2262543.368650875</v>
+        <v>2272517.816718026</v>
       </c>
       <c r="I6" s="8" t="n">
-        <v>2275971.008370179</v>
+        <v>2295822.974811531</v>
       </c>
       <c r="J6" s="9" t="n">
-        <v>2278253</v>
+        <v>2282633</v>
       </c>
       <c r="K6" s="9" t="inlineStr">
         <is>
-          <t>Selected 2,278,253. Late maturity (age 239 months). Incurred CL (2,269,176) and Paid CL (2,287,330) converge within 0.8% — midpoint selected. IE disqualified (negative IBNR, stale a priori). BF (2,262,543) is secondary and confirms the CL range. No prior selections.</t>
+          <t>Selected Incurred Chain Ladder ultimate of $2,282,633 (pct developed 98.2%). Paid CL ($2,314,707) and Incurred BF ($2,272,518) both converge within ~1.4%, reinforcing confidence in the CL-based estimate at this Tail maturity. IE is far below (a priori loss ratio understates this year) and is given no weight.</t>
         </is>
       </c>
       <c r="L6" s="10" t="n">
-        <v>2269176</v>
+        <v>2282633</v>
       </c>
       <c r="M6" s="10" t="inlineStr">
         <is>
-          <t>2,269,176 selected, following Incurred CL at 239 months (98.8% developed). This is a materially elevated year — incurred actual of 2,242,149 against an IE a priori of only 1,712,285, which produces a negative IBNR under IE and is clearly an artifact of a high-loss year exceeding the a priori. Paid CL of 2,287,330 agrees closely, confirming the CL indication is credible. BF of 2,262,543 also aligns. CL selected.</t>
+          <t>Selected $2,282,633 from Incurred Chain Ladder (CDF 1.018). Mature year with limited remaining development; CL tracks actual closely and BF ($2.27M) confirms via blend. IE ($1.71M) understates actual experience for this year and is not credible on its own.</t>
         </is>
       </c>
       <c r="N6" s="11" t="n"/>
@@ -816,34 +816,34 @@
         <v>1462141.027856</v>
       </c>
       <c r="E7" s="8" t="n">
-        <v>1540538.342238185</v>
+        <v>1551219.399558623</v>
       </c>
       <c r="F7" s="8" t="n">
-        <v>1499061.921059408</v>
+        <v>1513985.321864998</v>
       </c>
       <c r="G7" s="8" t="n">
         <v>1746530.9035</v>
       </c>
       <c r="H7" s="8" t="n">
-        <v>1543600.61516261</v>
+        <v>1555447.730806612</v>
       </c>
       <c r="I7" s="8" t="n">
-        <v>1505156.916698673</v>
+        <v>1521948.517630943</v>
       </c>
       <c r="J7" s="9" t="n">
-        <v>1523948</v>
+        <v>1551219</v>
       </c>
       <c r="K7" s="9" t="inlineStr">
         <is>
-          <t>Selected 1,523,948. Late maturity (age 227 months). Weighted 60% Incurred CL (1,540,538) + 40% Paid CL (1,499,062). IE methods disqualified for implausible IBNR at this maturity. BF (1,543,601) secondary and consistent with CL range. No prior selections.</t>
+          <t>Selected Incurred Chain Ladder ultimate of $1,551,219 (pct developed 97.8%). Paid CL is 2.4% lower and Incurred BF ($1,555,448) essentially matches CL, supporting the selection. Tail bucket: CL is primary; BF/IE receive no material weight at this maturity.</t>
         </is>
       </c>
       <c r="L7" s="10" t="n">
-        <v>1540538</v>
+        <v>1551219</v>
       </c>
       <c r="M7" s="10" t="inlineStr">
         <is>
-          <t>1,540,538 selected, following Incurred CL at 227 months (98.5% developed). Paid CL at 1,499,062 is somewhat lower, reflecting modest open case reserves (incurred actual 1,517,637 vs paid 1,462,141). Both BF methods (1,543,601 incurred, 1,505,157 paid) bracket the CL selections. Incurred CL is the primary selection given high maturity; the small divergence between incurred and paid is within normal range.</t>
+          <t>Selected $1,551,219 from Incurred Chain Ladder (CDF 1.022). Mature, stable development; BF ($1.56M) essentially agrees. IE ($1.75M) is a poor fit to this year's lower actual experience and is discounted.</t>
         </is>
       </c>
       <c r="N7" s="11" t="n"/>
@@ -863,34 +863,34 @@
         <v>4790693.153152</v>
       </c>
       <c r="E8" s="8" t="n">
-        <v>4898020.616126086</v>
+        <v>4931980.19864548</v>
       </c>
       <c r="F8" s="8" t="n">
-        <v>4936222.47941452</v>
+        <v>5000245.044129051</v>
       </c>
       <c r="G8" s="8" t="n">
         <v>2850338.4352</v>
       </c>
       <c r="H8" s="8" t="n">
-        <v>4861546.273480093</v>
+        <v>4880822.93622753</v>
       </c>
       <c r="I8" s="8" t="n">
-        <v>4874726.608658653</v>
+        <v>4910146.060709408</v>
       </c>
       <c r="J8" s="9" t="n">
-        <v>4917122</v>
+        <v>4931980</v>
       </c>
       <c r="K8" s="9" t="inlineStr">
         <is>
-          <t>Selected 4,917,122. Late maturity (age 215 months). Incurred CL (4,898,021) and Paid CL (4,936,222) converge within 0.8% — midpoint selected. IE disqualified (negative IBNR, stale a priori). BF (4,861,546) is secondary and confirms the CL range. No prior selections.</t>
+          <t>Selected Incurred Chain Ladder ultimate of $4,931,980 for this large-loss accident year (pct developed 97.5%). Paid CL independently confirms at $5,000,245 (+1.4%, convergence), and Incurred BF is close ($4,880,823). IE ($2,850,338) is far below both CL estimates, reflecting a priori loss ratios that do not capture the large claim(s) actually reported/paid this year -- disregarded as unrepresentative at this maturity. The two CL indications converging closely gives high confidence despite the large-loss volatility.</t>
         </is>
       </c>
       <c r="L8" s="10" t="n">
-        <v>4898021</v>
+        <v>4931980</v>
       </c>
       <c r="M8" s="10" t="inlineStr">
         <is>
-          <t>4,898,021 selected, following Incurred CL at 215 months (98.2% developed). This is a very large-loss year with incurred actual of 4,810,775 — roughly 3-4x the typical year. IE of 2,850,338 and BF of 4,861,546 are far below the actual, confirming the a priori badly underestimates this year. The CL development factor is minimal (1.018), so the CL ultimate is essentially the actual. Paid CL of 4,936,222 is close. Incurred CL selected.</t>
+          <t>Selected $4,931,980 from Incurred Chain Ladder (CDF 1.025). This is a large-loss accident year (actual incurred $4.81M vs. neighboring years around $1.5-2M); CL and BF ($4.88M) both track the actual large loss closely, while IE ($2.85M) is a generic a priori that badly understates the known large loss and is not used. High credibility given the size and near-full maturity of the loss.</t>
         </is>
       </c>
       <c r="N8" s="11" t="n"/>
@@ -910,34 +910,34 @@
         <v>1378427.939547998</v>
       </c>
       <c r="E9" s="8" t="n">
-        <v>1407636.755688367</v>
+        <v>1421635.833419866</v>
       </c>
       <c r="F9" s="8" t="n">
-        <v>1427402.652966397</v>
+        <v>1447354.71811471</v>
       </c>
       <c r="G9" s="8" t="n">
         <v>2543927.0535</v>
       </c>
       <c r="H9" s="8" t="n">
-        <v>1431215.064692266</v>
+        <v>1455745.722035926</v>
       </c>
       <c r="I9" s="8" t="n">
-        <v>1465711.018463087</v>
+        <v>1499576.331515699</v>
       </c>
       <c r="J9" s="9" t="n">
-        <v>1417520</v>
+        <v>1421636</v>
       </c>
       <c r="K9" s="9" t="inlineStr">
         <is>
-          <t>Selected 1,417,520. Late maturity (age 203 months). Incurred CL (1,407,637) and Paid CL (1,427,403) converge within 1.4% — midpoint selected. BF (1,431,215) is secondary and confirms the CL range. No prior selections.</t>
+          <t>Selected Incurred Chain Ladder ultimate of $1,421,636 (pct developed 97.0%). Paid CL is 1.8% higher, a converging signal. IE remains materially stale/high and is not weighted at this Tail maturity.</t>
         </is>
       </c>
       <c r="L9" s="10" t="n">
-        <v>1427403</v>
+        <v>1421636</v>
       </c>
       <c r="M9" s="10" t="inlineStr">
         <is>
-          <t>1,427,403 selected, following Paid CL at 203 months (96.6% developed). Incurred CL of 1,407,637 is slightly lower; both measures show the same actual (1,378,428), meaning all open reserves are on paid basis. Paid BF of 1,465,711 and Incurred BF of 1,431,215 support the range. Paid CL is chosen as a modest check on any case reserve strengthening; all indications are in a narrow band.</t>
+          <t>Selected $1,421,636 from Incurred Chain Ladder (CDF 1.031). Mature, well-behaved development; IE ($2.54M) appears to still reflect elevated a priori expectations (possibly anchored to the prior large-loss year) and overstates this normal year's actual experience, so CL/BF (BF $1.46M) is preferred.</t>
         </is>
       </c>
       <c r="N9" s="11" t="n"/>
@@ -957,34 +957,34 @@
         <v>1169581.089256</v>
       </c>
       <c r="E10" s="8" t="n">
-        <v>1197947.544886707</v>
+        <v>1217098.69912089</v>
       </c>
       <c r="F10" s="8" t="n">
-        <v>1217191.278030705</v>
+        <v>1244029.551167904</v>
       </c>
       <c r="G10" s="8" t="n">
         <v>2594805.5945</v>
       </c>
       <c r="H10" s="8" t="n">
-        <v>1231024.044818512</v>
+        <v>1270886.727002342</v>
       </c>
       <c r="I10" s="8" t="n">
-        <v>1271076.381259471</v>
+        <v>1324866.215151579</v>
       </c>
       <c r="J10" s="9" t="n">
-        <v>1207570</v>
+        <v>1217099</v>
       </c>
       <c r="K10" s="9" t="inlineStr">
         <is>
-          <t>Selected 1,207,570. Late maturity (age 191 months). Incurred CL (1,197,948) and Paid CL (1,217,191) converge within 1.6% — midpoint selected. BF (1,231,024) is secondary and confirms the CL range. No prior selections.</t>
+          <t>Selected Incurred Chain Ladder ultimate of $1,217,099 (pct developed 96.1%). Paid CL is 2.2% higher and Incurred BF close ($1,270,887); reasonable agreement across methods supports the CL-based selection.</t>
         </is>
       </c>
       <c r="L10" s="10" t="n">
-        <v>1217191</v>
+        <v>1217099</v>
       </c>
       <c r="M10" s="10" t="inlineStr">
         <is>
-          <t>1,217,191 selected, following Paid CL at 191 months (96.1% developed). Incurred CL of 1,197,948 is slightly lower. Actuals are identical for both measures (1,169,581), and CDFs are small. IE of 2,594,806 is far above actuals reflecting a low-loss year vs a priori — disregarded at this maturity. BF indications of 1,231,024 (incurred) and 1,271,076 (paid) are modestly above. Selecting paid CL as the anchor given high maturity.</t>
+          <t>Selected $1,217,099 from Incurred Chain Ladder (CDF 1.041). Mature year, actual experience is modest and stable; CL is highly credible at this maturity. IE ($2.59M) again overstates relative to observed experience and is disregarded.</t>
         </is>
       </c>
       <c r="N10" s="11" t="n"/>
@@ -1004,34 +1004,34 @@
         <v>1277672.072084001</v>
       </c>
       <c r="E11" s="8" t="n">
-        <v>1312586.094621001</v>
+        <v>1336229.09627828</v>
       </c>
       <c r="F11" s="8" t="n">
-        <v>1333006.53105774</v>
+        <v>1382103.968735571</v>
       </c>
       <c r="G11" s="8" t="n">
         <v>1134300.7311</v>
       </c>
       <c r="H11" s="8" t="n">
-        <v>1307843.808209848</v>
+        <v>1327380.071662524</v>
       </c>
       <c r="I11" s="8" t="n">
-        <v>1324758.050889469</v>
+        <v>1363379.934445764</v>
       </c>
       <c r="J11" s="9" t="n">
-        <v>1322796</v>
+        <v>1336229</v>
       </c>
       <c r="K11" s="9" t="inlineStr">
         <is>
-          <t>Selected 1,322,796. Mid maturity (age 179 months). Incurred CL (1,312,586) and Paid CL (1,333,007) converge within 1.5% — midpoint selected. Incurred IE disqualified (negative IBNR). BF (1,307,844) consistent with selection. No prior selections.</t>
+          <t>Selected Incurred Chain Ladder ultimate of $1,336,229 (pct developed 95.6%). Paid CL is 3.4% higher, Incurred BF nearly identical ($1,327,380). CL remains primary at this Tail maturity with no diagnostic signal to override.</t>
         </is>
       </c>
       <c r="L11" s="10" t="n">
-        <v>1312586</v>
+        <v>1336229</v>
       </c>
       <c r="M11" s="10" t="inlineStr">
         <is>
-          <t>1,312,586 selected, following Incurred CL at 179 months (97.3% developed). Paid CL of 1,333,007 is slightly above. IE of 1,134,301 is below actuals (low-loss year relative to a priori). BF methods of 1,307,844 (incurred) and 1,324,758 (paid) are close to CL. With 97%+ development, CL is highly credible; incurred CL selected given its slightly lower leverage and high maturity.</t>
+          <t>Selected $1,336,229 from Incurred Chain Ladder (CDF 1.046). Mature, stable development; BF ($1.33M) closely agrees, confirming the CL indication. IE ($1.13M) understates and is not credible relative to observed actual.</t>
         </is>
       </c>
       <c r="N11" s="11" t="n"/>
@@ -1051,34 +1051,34 @@
         <v>1892658.297732</v>
       </c>
       <c r="E12" s="8" t="n">
-        <v>1988125.368394688</v>
+        <v>2023936.544189146</v>
       </c>
       <c r="F12" s="8" t="n">
-        <v>1989436.782343472</v>
+        <v>2065782.963662511</v>
       </c>
       <c r="G12" s="8" t="n">
         <v>1542648.9944</v>
       </c>
       <c r="H12" s="8" t="n">
-        <v>1971982.621087207</v>
+        <v>1998288.876827237</v>
       </c>
       <c r="I12" s="8" t="n">
-        <v>1967702.26660322</v>
+        <v>2021941.28461947</v>
       </c>
       <c r="J12" s="9" t="n">
-        <v>1988781</v>
+        <v>2023937</v>
       </c>
       <c r="K12" s="9" t="inlineStr">
         <is>
-          <t>Selected 1,988,781. Mid maturity (age 167 months). Incurred CL (1,988,125) and Paid CL (1,989,437) converge within 0.1% — midpoint selected. Incurred IE disqualified (negative IBNR). BF (1,971,983) consistent with selection. No prior selections.</t>
+          <t>Selected Incurred Chain Ladder ultimate of $2,023,937 (pct developed 94.7%). Paid CL is 2.1% higher and Incurred BF close ($1,998,289); consistent cross-method agreement supports this selection.</t>
         </is>
       </c>
       <c r="L12" s="10" t="n">
-        <v>1988125</v>
+        <v>2023937</v>
       </c>
       <c r="M12" s="10" t="inlineStr">
         <is>
-          <t>1,988,125 selected, following Incurred CL at 167 months (96.4% developed). Paid CL of 1,989,437 agrees almost exactly, which is reassuring. This is an elevated year vs a priori (IE of 1,542,649 would imply negative IBNR). BF indications of 1,971,983 (incurred) and 1,967,702 (paid) are also very close to CL. Strong convergence across all methods supports CL selection.</t>
+          <t>Selected $2,023,937 from Incurred Chain Ladder (CDF 1.056). Mature year with a somewhat higher actual loss level; CL and BF ($2.00M) agree closely. IE ($1.54M) is well below actual experience and given no weight.</t>
         </is>
       </c>
       <c r="N12" s="11" t="n"/>
@@ -1098,34 +1098,34 @@
         <v>1194236.878339999</v>
       </c>
       <c r="E13" s="8" t="n">
-        <v>1422105.031111689</v>
+        <v>1443399.191869474</v>
       </c>
       <c r="F13" s="8" t="n">
-        <v>1267855.567590908</v>
+        <v>1313903.557982452</v>
       </c>
       <c r="G13" s="8" t="n">
         <v>1573501.9744</v>
       </c>
       <c r="H13" s="8" t="n">
-        <v>1428317.1331297</v>
+        <v>1450578.177232828</v>
       </c>
       <c r="I13" s="8" t="n">
-        <v>1285603.084278704</v>
+        <v>1337547.059321948</v>
       </c>
       <c r="J13" s="9" t="n">
-        <v>1368118</v>
+        <v>1443399</v>
       </c>
       <c r="K13" s="9" t="inlineStr">
         <is>
-          <t>Selected 1,368,118. Mid maturity (age 155 months). Weighted 65% Incurred CL (1,422,105) + 35% Paid CL (1,267,856). Incurred BF (1,428,317) within 4% of selection, confirming range. No prior selections.</t>
+          <t>Selected Incurred Chain Ladder ultimate of $1,443,399 (pct developed 94.5%). Paid-based indications run consistently lower across all methods (Paid CL $1,313,904, Paid BF $1,337,547 vs. Incurred CL $1,443,399, Incurred BF $1,450,578), suggesting paid development is lagging incurred at this maturity rather than incurred being overstated. Incurred CL retained as primary per Tail-bucket convention absent evidence of case-reserve inadequacy.</t>
         </is>
       </c>
       <c r="L13" s="10" t="n">
-        <v>1422105</v>
+        <v>1443399</v>
       </c>
       <c r="M13" s="10" t="inlineStr">
         <is>
-          <t>1,422,105 selected, following Incurred CL at 155 months (95.9% developed). Paid CL of 1,267,856 is notably lower, reflecting incurred actual of 1,363,753 vs paid actual of 1,194,237 — a meaningful gap suggesting open case reserves. At 155 months with a CDF of 1.043, incurred CL is more reliable as it captures open case development. Incurred BF of 1,428,317 agrees closely. Paid BF of 1,285,603 is higher than paid CL but still below incurred, consistent with the open reserve picture.</t>
+          <t>Selected $1,443,399 from Incurred Chain Ladder (CDF 1.058). Reasonably mature; CL, IE ($1.57M) and BF ($1.45M) are all fairly close here, increasing confidence in the CL-based selection as the most data-driven of the three.</t>
         </is>
       </c>
       <c r="N13" s="11" t="n"/>
@@ -1145,34 +1145,34 @@
         <v>708529.9908599999</v>
       </c>
       <c r="E14" s="8" t="n">
-        <v>742540.4765075424</v>
+        <v>752159.2288710807</v>
       </c>
       <c r="F14" s="8" t="n">
-        <v>763490.4060157106</v>
+        <v>793558.6435852194</v>
       </c>
       <c r="G14" s="8" t="n">
         <v>1203729.0102</v>
       </c>
       <c r="H14" s="8" t="n">
-        <v>763664.2354165952</v>
+        <v>778352.6792895264</v>
       </c>
       <c r="I14" s="8" t="n">
-        <v>795181.3038487363</v>
+        <v>837507.8008944974</v>
       </c>
       <c r="J14" s="9" t="n">
-        <v>749872</v>
+        <v>752159</v>
       </c>
       <c r="K14" s="9" t="inlineStr">
         <is>
-          <t>Selected 749,872. Mid maturity (age 143 months). Weighted 65% Incurred CL (742,540) + 35% Paid CL (763,490). Incurred BF (763,664) within 2% of selection, confirming range. No prior selections.</t>
+          <t>Selected Incurred Chain Ladder ultimate of $752,159 (pct developed 94.2%). Paid CL runs 5.4% higher ($793,559); moderate but not disqualifying divergence. Incurred CL retained as primary Tail-bucket method; IE ($1,203,729) is stale and disregarded.</t>
         </is>
       </c>
       <c r="L14" s="10" t="n">
-        <v>742540</v>
+        <v>752159</v>
       </c>
       <c r="M14" s="10" t="inlineStr">
         <is>
-          <t>742,540 selected, following Incurred CL at 143 months (95.4% developed). Paid CL of 763,490 is close. Both actuals are 708,530 (same for incurred and paid), indicating minimal open reserves. BF methods of 763,664 (incurred) and 795,181 (paid) are slightly higher. IE of 1,203,729 is far above and not credible relative to actuals at this maturity. CL is the primary selection; incurred CL chosen.</t>
+          <t>Selected $752,159 from Incurred Chain Ladder (CDF 1.062). This is a genuinely low actual-experience year; IE ($1.20M) is a generic a priori that overstates it substantially, pulling BF ($778K) up with it. CL is preferred as the best reflection of this year's real (low) loss activity at a reasonably mature age.</t>
         </is>
       </c>
       <c r="N14" s="11" t="n"/>
@@ -1192,34 +1192,34 @@
         <v>1389603.684732</v>
       </c>
       <c r="E15" s="8" t="n">
-        <v>1499995.914631738</v>
+        <v>1489923.195802261</v>
       </c>
       <c r="F15" s="8" t="n">
-        <v>1512368.68741561</v>
+        <v>1589049.725515616</v>
       </c>
       <c r="G15" s="8" t="n">
         <v>1227803.5905</v>
       </c>
       <c r="H15" s="8" t="n">
-        <v>1479963.914991344</v>
+        <v>1472274.158106936</v>
       </c>
       <c r="I15" s="8" t="n">
-        <v>1489269.402712616</v>
+        <v>1543708.720624237</v>
       </c>
       <c r="J15" s="9" t="n">
-        <v>1506182</v>
+        <v>1489923</v>
       </c>
       <c r="K15" s="9" t="inlineStr">
         <is>
-          <t>Selected 1,506,182. Mid maturity (age 131 months). Incurred CL (1,499,996) and Paid CL (1,512,369) converge within 0.8% — midpoint selected. Incurred IE disqualified (negative IBNR). BF (1,479,964) consistent with selection. No prior selections.</t>
+          <t>Selected Incurred Chain Ladder ultimate of $1,489,923 (pct developed 93.3%). Paid CL is 6.7% higher ($1,589,050); Incurred BF is close to Incurred CL ($1,472,274), supporting the incurred-side selection as primary at this Tail maturity.</t>
         </is>
       </c>
       <c r="L15" s="10" t="n">
-        <v>1499996</v>
+        <v>1489923</v>
       </c>
       <c r="M15" s="10" t="inlineStr">
         <is>
-          <t>1,499,996 selected, following Incurred CL at 131 months (92.6% developed). Paid CL of 1,512,369 is close. Both actuals are identical (1,389,604), and BF methods (1,479,964 incurred, 1,489,269 paid) are slightly below CL. IE of 1,227,804 implies negative IBNR — this is an elevated-loss year vs the a priori. All development methods agree within ~1%; incurred CL is the primary anchor with BF as a modest check.</t>
+          <t>Selected $1,489,923 from Incurred Chain Ladder (CDF 1.072). Reasonably mature with clean development; BF ($1.47M) is close. IE ($1.23M) understates relative to actual and is not used.</t>
         </is>
       </c>
       <c r="N15" s="11" t="n"/>
@@ -1239,34 +1239,34 @@
         <v>3364231.298548001</v>
       </c>
       <c r="E16" s="8" t="n">
-        <v>3679098.836333144</v>
+        <v>3634443.543222012</v>
       </c>
       <c r="F16" s="8" t="n">
-        <v>3698059.893148677</v>
+        <v>3924032.080420801</v>
       </c>
       <c r="G16" s="8" t="n">
         <v>1669812.8832</v>
       </c>
       <c r="H16" s="8" t="n">
-        <v>3517368.726845768</v>
+        <v>3498503.646862821</v>
       </c>
       <c r="I16" s="8" t="n">
-        <v>3514967.442404812</v>
+        <v>3602446.10883477</v>
       </c>
       <c r="J16" s="9" t="n">
-        <v>3688580</v>
+        <v>3634444</v>
       </c>
       <c r="K16" s="9" t="inlineStr">
         <is>
-          <t>Selected 3,688,580. Early-mid maturity (age 119 months). Incurred CL (3,679,099) and Paid CL (3,698,060) converge within 0.5%. Incurred IE disqualified (negative IBNR). BF (3,517,369) and IE (1,669,813 if credible) consistent. No prior selections.</t>
+          <t>Selected Incurred Chain Ladder ultimate of $3,634,444 for this large-loss accident year (pct developed 93.1%). Paid CL runs materially higher ($3,924,032, +8.0%), likely reflecting a large claim settling into paid more recently; Incurred BF ($3,498,504) brackets the two. Incurred CL retained as primary per Tail convention; the paid-side elevation is noted as a monitoring item but does not override in the absence of a confirmed case-adequacy diagnostic.</t>
         </is>
       </c>
       <c r="L16" s="10" t="n">
-        <v>3517369</v>
+        <v>3634444</v>
       </c>
       <c r="M16" s="10" t="inlineStr">
         <is>
-          <t>3,517,369 selected, following Incurred BF at 119 months (91.9% developed). This is a very elevated year — incurred actual of 3,382,963 with CL projecting 3,679,099 and IE implying a negative IBNR of -1.71M (a priori of 1,669,813 is far below actuals). The BF credibly blends the high actual with a modest development load: incurred BF at 3,517,369 is preferred over the CL at 3,679,099 as a tempering measure given the year's obvious outlier characteristics. Paid CL of 3,698,060 and paid BF of 3,514,967 bracket this selection. Selecting incurred BF.</t>
+          <t>Selected $3,634,444 from Incurred Chain Ladder (CDF 1.074). Another elevated-loss accident year (actual $3.38M, well above the surrounding years); CL tracks the large actual experience appropriately. IE ($1.67M) badly understates this year's known large losses and is disregarded; BF ($3.50M), while a reasonable fallback, is unnecessarily diluted by the non-credible IE component.</t>
         </is>
       </c>
       <c r="N16" s="11" t="n"/>
@@ -1286,34 +1286,34 @@
         <v>2462208.676391999</v>
       </c>
       <c r="E17" s="8" t="n">
-        <v>2829297.908610753</v>
+        <v>2827268.770706758</v>
       </c>
       <c r="F17" s="8" t="n">
-        <v>2855389.845633978</v>
+        <v>3001151.021268567</v>
       </c>
       <c r="G17" s="8" t="n">
         <v>2554813.7112</v>
       </c>
       <c r="H17" s="8" t="n">
-        <v>2797964.576157609</v>
+        <v>2796340.291365324</v>
       </c>
       <c r="I17" s="8" t="n">
-        <v>2814001.14483584</v>
+        <v>2920998.414888707</v>
       </c>
       <c r="J17" s="9" t="n">
-        <v>2842344</v>
+        <v>2827269</v>
       </c>
       <c r="K17" s="9" t="inlineStr">
         <is>
-          <t>Selected 2,842,344. Early-mid maturity (age 107 months). Incurred CL (2,829,298) and Paid CL (2,855,390) converge within 0.9%. BF (2,797,965) and IE (2,554,814 if credible) consistent. No prior selections.</t>
+          <t>Selected Incurred Chain Ladder ultimate of $2,827,269 (pct developed 88.7%). Paid CL runs 6.1% higher and Incurred BF is essentially identical to Incurred CL ($2,796,340), supporting the selection. IE ($2,554,814) is reasonably close, providing secondary support.</t>
         </is>
       </c>
       <c r="L17" s="10" t="n">
-        <v>2829298</v>
+        <v>2796340</v>
       </c>
       <c r="M17" s="10" t="inlineStr">
         <is>
-          <t>2,829,298 selected, following Incurred CL at 107 months (88.6% developed). Paid CL of 2,855,390 agrees closely. IE of 2,554,814 and incurred BF of 2,797,965 are modestly below CL. At 107 months, incurred CL is still highly credible and the spread between methods is modest (roughly 10%). The incurred CL is the primary selection as the book is well-developed at this age.</t>
+          <t>Selected $2,796,340 from Incurred Benktander (blend of CL $2.83M and IE $2.55M). At 107 months (~89% developed), roughly 11% of ultimate loss remains to emerge; unlike earlier years, IE ($2.55M) is reasonably close to CL here, lending it some credibility, so a BF blend is used for modest additional stability versus pure CL. Values are close (within ~1%) regardless of method chosen.</t>
         </is>
       </c>
       <c r="N17" s="11" t="n"/>
@@ -1333,34 +1333,34 @@
         <v>1205811.828916</v>
       </c>
       <c r="E18" s="8" t="n">
-        <v>1381615.222830049</v>
+        <v>1381984.566296623</v>
       </c>
       <c r="F18" s="8" t="n">
-        <v>1416542.270584225</v>
+        <v>1494732.528127032</v>
       </c>
       <c r="G18" s="8" t="n">
         <v>2605909.9854</v>
       </c>
       <c r="H18" s="8" t="n">
-        <v>1537400.401550151</v>
+        <v>1538008.227263389</v>
       </c>
       <c r="I18" s="8" t="n">
-        <v>1593477.325085412</v>
+        <v>1709514.880060673</v>
       </c>
       <c r="J18" s="9" t="n">
-        <v>1421504</v>
+        <v>1381985</v>
       </c>
       <c r="K18" s="9" t="inlineStr">
         <is>
-          <t>Selected 1,421,504. Early-mid maturity (age 95 months). Weighted 55% Incurred CL (1,381,615) + 25% Paid CL (1,416,542) + 20% Incurred BF (1,537,400). Incurred CL is primary at this maturity; BF provides a credibility check. No prior selections.</t>
+          <t>Selected Incurred Chain Ladder ultimate of $1,381,985 (pct developed 87.3%). Paid CL runs notably higher ($1,494,733, +8.2%) and Paid BF higher still ($1,709,515), while Incurred BF ($1,538,008) also sits above Incurred CL -- a pattern suggesting some upward pressure on this year. Retained Incurred CL as primary per Tail convention but flagged for monitoring given the consistent paid-side elevation; no confirmed diagnostic (e.g., case-reserve strengthening) available to justify an override this cycle.</t>
         </is>
       </c>
       <c r="L18" s="10" t="n">
-        <v>1537400</v>
+        <v>1381985</v>
       </c>
       <c r="M18" s="10" t="inlineStr">
         <is>
-          <t>1,537,400 selected, following Incurred BF at 95 months (87.3% developed). Incurred CL of 1,381,615 appears low relative to the a priori trend — the IE of 2,605,910 is very high but the actual of 1,205,812 is small, suggesting either a low-loss year or immature paid/incurred. Paid CL of 1,416,542 is close to incurred CL. Paid BF of 1,593,477 and incurred BF of 1,537,400 credibly temper the outlier CL direction. At 95 months with ~87% development, BF is the appropriate anchor. Selecting incurred BF as the primary indication.</t>
+          <t>Selected $1,381,985 from Incurred Chain Ladder (CDF 1.146, ~87% developed). Actual experience is on the lower side this year; IE ($2.61M) is a stale, much higher a priori that does not fit the observed pattern and pulls BF ($1.54M) up artificially. CL is preferred as more reflective of actual emergence at this maturity.</t>
         </is>
       </c>
       <c r="N18" s="11" t="n"/>
@@ -1380,34 +1380,34 @@
         <v>2395448.423304001</v>
       </c>
       <c r="E19" s="8" t="n">
-        <v>2768026.838982237</v>
+        <v>2786612.107331773</v>
       </c>
       <c r="F19" s="8" t="n">
-        <v>2898504.960110452</v>
+        <v>3055527.135382659</v>
       </c>
       <c r="G19" s="8" t="n">
         <v>2215023.4875</v>
       </c>
       <c r="H19" s="8" t="n">
-        <v>2693592.187678146</v>
+        <v>2706376.788719082</v>
       </c>
       <c r="I19" s="8" t="n">
-        <v>2779881.798406536</v>
+        <v>2873955.006970741</v>
       </c>
       <c r="J19" s="9" t="n">
-        <v>2785760</v>
+        <v>2786612</v>
       </c>
       <c r="K19" s="9" t="inlineStr">
         <is>
-          <t>Selected 2,785,760. Early-mid maturity (age 83 months). Weighted 55% Incurred CL (2,768,027) + 25% Paid CL (2,898,505) + 20% Incurred BF (2,693,592). Incurred IE disqualified (negative IBNR, stale a priori). Paid IE disqualified (negative IBNR). Incurred CL is primary at this maturity; BF provides a credibility check. No prior selections.</t>
+          <t>Selected Incurred Chain Ladder ultimate of $2,786,612 (pct developed 86.0%, Late bucket). Paid CL is notably higher ($3,055,527, +9.6%), while Incurred BF is close to Incurred CL ($2,706,377). Both Paid CL and Incurred CL are primary methods at this maturity per the framework; incurred is retained given its closer agreement with the BF cross-check, with the paid-side elevation noted as a watch item absent a confirmed diagnostic.</t>
         </is>
       </c>
       <c r="L19" s="10" t="n">
-        <v>2768027</v>
+        <v>2706377</v>
       </c>
       <c r="M19" s="10" t="inlineStr">
         <is>
-          <t>2,768,027 selected, following Incurred CL at 83 months (86.5% developed). Incurred actual is 2,395,448 with a modest development factor of 1.156. Paid CL of 2,898,505 is higher, reflecting a larger gap between incurred and paid actuals (2,395,448 vs 2,395,448 — same, but paid CDF is 1.21 vs incurred 1.156). Incurred BF of 2,693,592 and paid BF of 2,779,882 bracket the incurred CL. The IE a priori of 2,215,023 implies a negative IBNR, suggesting this is above the a priori. Incurred CL is the primary selection with BF as a check; selecting incurred CL.</t>
+          <t>Selected $2,706,377 from Incurred Benktander (blend of CL $2.79M and IE $2.22M). At 83 months (~86% developed), meaningful development remains; CL and IE are reasonably close here (unlike 2017), so a BF blend is used to temper the CL point estimate with a modest amount of a priori credibility while remaining close to the data-driven indication.</t>
         </is>
       </c>
       <c r="N19" s="11" t="n"/>
@@ -1427,34 +1427,34 @@
         <v>2395189.834488001</v>
       </c>
       <c r="E20" s="8" t="n">
-        <v>3229577.567630864</v>
+        <v>3287554.965413234</v>
       </c>
       <c r="F20" s="8" t="n">
-        <v>3231484.153933392</v>
+        <v>3324054.652636242</v>
       </c>
       <c r="G20" s="8" t="n">
         <v>2259323.9575</v>
       </c>
       <c r="H20" s="8" t="n">
-        <v>3040400.024531793</v>
+        <v>3072475.438285537</v>
       </c>
       <c r="I20" s="8" t="n">
-        <v>2979893.240551207</v>
+        <v>3026529.194464179</v>
       </c>
       <c r="J20" s="9" t="n">
-        <v>3113619</v>
+        <v>3287555</v>
       </c>
       <c r="K20" s="9" t="inlineStr">
         <is>
-          <t>Selected 3,113,619. Green-to-early maturity (age 71 months). Weighted 35% Incurred BF (3,040,400) + 35% Incurred CL (3,229,578) + 20% Paid BF (2,979,893) + 10% Paid CL (3,231,484). Incurred IE disqualified (negative IBNR). Paid IE disqualified (negative IBNR). BF methods are primary at this maturity; CL provides a secondary check. No prior selections.</t>
+          <t>Selected Incurred Chain Ladder ultimate of $3,287,555 (pct developed 79.1%, Late bucket). Paid CL closely confirms at $3,324,055 (+1.1%, convergence), giving high confidence in this estimate for a year with an elevated reported loss (2019 shows relatively heavier activity than 2018/2020).</t>
         </is>
       </c>
       <c r="L20" s="10" t="n">
-        <v>3040400</v>
+        <v>3072475</v>
       </c>
       <c r="M20" s="10" t="inlineStr">
         <is>
-          <t>3,040,400 selected, following Incurred BF at 71 months (80.5% developed). Incurred CL of 3,229,578 and paid CL of 3,231,484 both indicate around 3.23M — elevated relative to the a priori IE of 2,259,324. At 71 months (~80% developed), CL carries moderate leverage and the BF appropriately tempers the indication. Incurred BF of 3,040,400 and paid BF of 2,979,893 are close; selecting incurred BF as it blends actual experience with a priori. The convergence of incurred and paid CL is reassuring that the underlying experience is real.</t>
+          <t>Selected $3,072,475 from Incurred Benktander (blend of CL $3.29M and IE $2.26M). At 71 months (~79% developed), roughly a fifth of ultimate loss remains unreported; BF moderates CL's higher leverage at this maturity by incorporating a priori credibility, producing a more stable estimate than relying on CL alone.</t>
         </is>
       </c>
       <c r="N20" s="11" t="n"/>
@@ -1474,34 +1474,34 @@
         <v>976050.862556</v>
       </c>
       <c r="E21" s="8" t="n">
-        <v>1325429.234341166</v>
+        <v>1367790.642482181</v>
       </c>
       <c r="F21" s="8" t="n">
-        <v>1461697.550610732</v>
+        <v>1523888.486705368</v>
       </c>
       <c r="G21" s="8" t="n">
         <v>1843608.3492</v>
       </c>
       <c r="H21" s="8" t="n">
-        <v>1460905.698459077</v>
+        <v>1503075.445087571</v>
       </c>
       <c r="I21" s="8" t="n">
-        <v>1588586.806455568</v>
+        <v>1638827.717095581</v>
       </c>
       <c r="J21" s="9" t="n">
-        <v>1439104</v>
+        <v>1421905</v>
       </c>
       <c r="K21" s="9" t="inlineStr">
         <is>
-          <t>Selected 1,439,104. Green-to-early maturity (age 59 months). Weighted 35% Incurred BF (1,460,906) + 35% Incurred CL (1,325,429) + 20% Paid BF (1,588,587) + 10% Paid CL (1,461,698). BF methods are primary at this maturity; CL provides a secondary check. No prior selections.</t>
+          <t>Selected a 60%/40% blend of Incurred CL ($1,367,791) and Incurred BF ($1,503,075) = $1,421,905 (Mid maturity, age 59mo, pct developed 71.6%). Pure Incurred CL sits as a low outlier relative to Paid CL ($1,523,888), Paid BF ($1,638,828), and IE ($1,843,608), all of which point higher; per the Mid-maturity table CL is primary but BF carries meaningful secondary weight (0-40%), used here to temper the CL indication given the consistent upward signal from other methods.</t>
         </is>
       </c>
       <c r="L21" s="10" t="n">
-        <v>1460906</v>
+        <v>1503075</v>
       </c>
       <c r="M21" s="10" t="inlineStr">
         <is>
-          <t>1,460,906 selected, following Incurred BF at 59 months (73.9% developed). Incurred CL of 1,325,429 is below both BF methods (incurred BF 1,460,906, paid BF 1,588,587), and paid CL of 1,461,698 aligns with incurred BF. At 59 months with ~74% development, BF is the most credible method. IE of 1,843,608 is above all CL/BF indications. Incurred BF at 1,460,906 is selected as a balanced estimate, consistent with paid CL and well within the range of all indications.</t>
+          <t>Selected $1,503,075 from Incurred Benktander (blend of CL $1.37M and IE $1.84M). At 59 months (~72% developed), substantial development remains and CL is not yet fully credible on its own; IE is notably higher than actual-to-date, and BF appropriately balances the two, giving weight to the a priori given the immaturity.</t>
         </is>
       </c>
       <c r="N21" s="11" t="n"/>
@@ -1521,34 +1521,34 @@
         <v>974979.4133360002</v>
       </c>
       <c r="E22" s="8" t="n">
-        <v>1436414.01140312</v>
+        <v>1465365.572125121</v>
       </c>
       <c r="F22" s="8" t="n">
-        <v>1576900.427061856</v>
+        <v>1674437.220160199</v>
       </c>
       <c r="G22" s="8" t="n">
         <v>1410360.3873</v>
       </c>
       <c r="H22" s="8" t="n">
-        <v>1428703.550087028</v>
+        <v>1448321.886414044</v>
       </c>
       <c r="I22" s="8" t="n">
-        <v>1513330.180114698</v>
+        <v>1564125.170164199</v>
       </c>
       <c r="J22" s="9" t="n">
-        <v>1469786</v>
+        <v>1456844</v>
       </c>
       <c r="K22" s="9" t="inlineStr">
         <is>
-          <t>Selected 1,469,786. Green maturity (age 47 months). Weighted 40% Incurred BF (1,428,704) + 25% Incurred CL (1,436,414) + 20% Paid BF (1,513,330) + 15% Paid CL (1,576,900). BF is primary at this early maturity; CL is heavily discounted due to high CDFs and volatile link ratios. No prior selections.</t>
+          <t>Selected the average of Incurred CL ($1,465,366) and Incurred BF ($1,448,322) = $1,456,844 (Mid maturity, age 47mo). These two primary methods converge within 1.2%, giving high confidence; Paid CL runs materially higher (+14.3%) but is still developing at only 58.2% and is given less weight at this maturity.</t>
         </is>
       </c>
       <c r="L22" s="10" t="n">
-        <v>1513330</v>
+        <v>1448322</v>
       </c>
       <c r="M22" s="10" t="inlineStr">
         <is>
-          <t>1,513,330 selected, following Paid BF at 47 months (61.8% developed). At only 47 months of development, the book is approximately 60-70% developed and CL is quite leveraged. Incurred CL of 1,436,414 and paid CL of 1,576,900 bracket the BF indications (incurred BF 1,428,704, paid BF 1,513,330). IE of 1,410,360 is the a priori anchor. The paid BF of 1,513,330 best balances the credibility split at this maturity — paid losses are less subject to case reserve adequacy uncertainty, and blending with the a priori through BF is appropriate. Paid BF selected.</t>
+          <t>Selected $1,448,322 from Incurred Benktander (blend of CL $1.47M and IE $1.41M). At 47 months (~69% developed), meaningful development remains, but CL and IE converge closely here, giving good confidence in the BF blend as a stable, well-supported estimate.</t>
         </is>
       </c>
       <c r="N22" s="11" t="n"/>
@@ -1568,34 +1568,34 @@
         <v>791103.7101360001</v>
       </c>
       <c r="E23" s="8" t="n">
-        <v>1369127.263774071</v>
+        <v>1348766.48847748</v>
       </c>
       <c r="F23" s="8" t="n">
-        <v>1509816.800574681</v>
+        <v>1555651.569268913</v>
       </c>
       <c r="G23" s="8" t="n">
         <v>959045.0632</v>
       </c>
       <c r="H23" s="8" t="n">
-        <v>1206873.462196073</v>
+        <v>1198124.09365756</v>
       </c>
       <c r="I23" s="8" t="n">
-        <v>1247634.754816436</v>
+        <v>1262440.521261474</v>
       </c>
       <c r="J23" s="9" t="n">
-        <v>1301030</v>
+        <v>1273445</v>
       </c>
       <c r="K23" s="9" t="inlineStr">
         <is>
-          <t>Selected 1,301,030. Green maturity (age 35 months). Weighted 40% Incurred BF (1,206,873) + 25% Incurred CL (1,369,127) + 20% Paid BF (1,247,635) + 15% Paid CL (1,509,817). BF is primary at this early maturity; CL is heavily discounted due to high CDFs and volatile link ratios. No prior selections.</t>
+          <t>Selected the average of Incurred CL ($1,348,766) and Incurred BF ($1,198,124) = $1,273,445 (Early maturity, age 35mo, pct developed 61.4%). Per the Early-maturity table, Incurred BF and Incurred CL are co-primary; blending dampens CL's greater volatility at this immature stage. Paid-side methods and IE are secondary/low-credibility here and were not weighted directly.</t>
         </is>
       </c>
       <c r="L23" s="10" t="n">
-        <v>1247635</v>
+        <v>1198124</v>
       </c>
       <c r="M23" s="10" t="inlineStr">
         <is>
-          <t>1,247,635 selected, following Paid BF at 35 months (52.4% developed). At 35 months, the year is just over half-developed. Incurred CL of 1,369,127 and paid CL of 1,509,817 are highly leveraged. Incurred BF of 1,206,873 and paid BF of 1,247,635 are much more stable. The IE a priori of 959,045 appears low. Paid BF at 1,247,635 is selected as a credible blend between the leveraged CL and the a priori — it uses the more stable paid development while tempering with expected losses.</t>
+          <t>Selected $1,198,124 from Incurred Benktander (blend of CL $1.35M and IE $959K). At only 35 months (~61% developed), CL carries high leverage and limited credibility on its own; BF tempers the CL estimate with a priori weight appropriate for this immaturity, avoiding over-reliance on a still-thin actual base.</t>
         </is>
       </c>
       <c r="N23" s="11" t="n"/>
@@ -1615,34 +1615,34 @@
         <v>1199242.068356001</v>
       </c>
       <c r="E24" s="8" t="n">
-        <v>3279798.511752855</v>
+        <v>3284873.860379293</v>
       </c>
       <c r="F24" s="8" t="n">
-        <v>3158470.126475578</v>
+        <v>3160025.325928244</v>
       </c>
       <c r="G24" s="8" t="n">
         <v>978225.9645999999</v>
       </c>
       <c r="H24" s="8" t="n">
-        <v>2137333.087382769</v>
+        <v>2138094.263711344</v>
       </c>
       <c r="I24" s="8" t="n">
-        <v>1806044.627911641</v>
+        <v>1806227.423116317</v>
       </c>
       <c r="J24" s="9" t="n">
-        <v>1806125</v>
+        <v>2138094</v>
       </c>
       <c r="K24" s="9" t="inlineStr">
         <is>
-          <t>Selected 1,806,125. Very green maturity (age 23 months). Weighted 50% Incurred BF (2,137,333) + 30% Paid BF (1,806,045) + 20% Incurred IE (978,226). CL methods disqualified: Incurred CDF=1.986 and Paid CDF=2.634 are too volatile for CL reliance at 11 months. BF methods are primary; IE is secondary and shows positive IBNR (credible). No prior selections.</t>
+          <t>Selected Incurred BF ultimate of $2,138,094 (Green maturity, age 23mo, pct developed 50.3%). Incurred CL ($3,284,874) is an outlier driven by limited, volatile early development at this maturity and is disqualified as primary per the Green-bucket screen (BF/Benktander preferred over raw CL for long-tail lines this immature). Paid BF ($1,806,227) was considered but paid data is even less mature (37.9% developed) and less credible; Incurred BF -- which blends the a priori (IE $978,226) with actual incurred experience -- is selected as the most balanced estimate.</t>
         </is>
       </c>
       <c r="L24" s="10" t="n">
-        <v>2137333</v>
+        <v>2138094</v>
       </c>
       <c r="M24" s="10" t="inlineStr">
         <is>
-          <t>2,137,333 selected, following Incurred BF at 23 months (50.4% developed). This is the most uncertain year other than 2024. Incurred CL of 3,279,799 and paid CL of 3,158,470 are extremely leveraged (CDFs of 1.99 and 2.63 respectively). The incurred BF of 2,137,333 and paid BF of 1,806,045 bracket a credible range. The incurred actual of 1,651,757 is meaningfully higher than the paid actual of 1,199,242, suggesting significant open case reserves this early. The incurred BF of 2,137,333 — which uses the incurred development pattern blended with the a priori — is preferred as it captures the case reserve signal while moderating the extreme CL leverage. IE methods (978,226) appear implausibly low given actuals already at 1.65M incurred.</t>
+          <t>Selected $2,138,094 from Incurred Benktander (blend of CL $3.28M and IE $978K). At 23 months (~50% developed), CL is highly leveraged (nearly doubling actual reported-to-date) and not credible on a standalone basis; BF appropriately blends substantial a priori credibility with the emerging actual experience, producing a materially more stable and defensible estimate than either extreme.</t>
         </is>
       </c>
       <c r="N24" s="11" t="n"/>
@@ -1662,34 +1662,34 @@
         <v>355247.7609319999</v>
       </c>
       <c r="E25" s="8" t="n">
-        <v>2969450.702244298</v>
+        <v>3009451.107995131</v>
       </c>
       <c r="F25" s="8" t="n">
-        <v>2385840.731008563</v>
+        <v>2389355.706658277</v>
       </c>
       <c r="G25" s="8" t="n">
         <v>997790.4838</v>
       </c>
       <c r="H25" s="8" t="n">
-        <v>1588837.049345689</v>
+        <v>1592812.680510819</v>
       </c>
       <c r="I25" s="8" t="n">
-        <v>1204468.882727955</v>
+        <v>1204687.442772524</v>
       </c>
       <c r="J25" s="9" t="n">
-        <v>1355317</v>
+        <v>1238366</v>
       </c>
       <c r="K25" s="9" t="inlineStr">
         <is>
-          <t>Selected 1,355,317. Very green maturity (age 11 months). Weighted 50% Incurred BF (1,588,837) + 30% Paid BF (1,204,469) + 20% Incurred IE (997,790). CL methods disqualified: Incurred CDF=3.336 and Paid CDF=6.716 are too volatile for CL reliance at 11 months. BF methods are primary; IE is secondary and shows positive IBNR (credible). No prior selections.</t>
+          <t>Selected a blend weighting the average of Incurred BF ($1,592,813) and Paid BF ($1,204,687) at 60% and IE/a-priori ($997,790) at 40%, = $1,238,366 (Very Green maturity, age 11mo, pct developed only 29.6% incurred / 14.9% paid). Chain Ladder is disqualified at this maturity (CDF of 3.38x incurred / 6.73x paid makes CL estimates highly unstable and is given zero weight per the Very-Green screen). BF and a priori/IE are the primary methods per the framework; the blend leans toward BF since it already incorporates actual reported/paid experience with credibility, while IE anchors the estimate given the very limited maturity.</t>
         </is>
       </c>
       <c r="L25" s="10" t="n">
-        <v>1204469</v>
+        <v>1592813</v>
       </c>
       <c r="M25" s="10" t="inlineStr">
         <is>
-          <t>1,204,469 selected, following Paid BF at 11 months (14.9% developed). At 11 months the year is barely begun — paid CDF of 6.716 and incurred CDF of 3.336 are both extremely leveraged and CL indications (2,969,451 incurred, 2,385,841 paid) are unreliable. The IE a priori of 997,790 is a reasonable anchor. Incurred BF of 1,588,837 and paid BF of 1,204,469 reflect where the a priori dominates but is tempered by early actuals. Paid BF is preferred because paid losses at 11 months are the cleanest signal — incurred at this age is heavily influenced by early case reserve adequacy. Paid BF of 1,204,469 is selected as the most defensible low-maturity estimate.</t>
+          <t>Selected $1,592,813 from Incurred Benktander (blend of CL $3.01M and IE $998K). At only 11 months (~30% developed), CL is extremely leveraged and unreliable this early, while IE reflects the a priori expectation with no development risk. BF is the appropriate credibility-weighted approach at this maturity, balancing the very immature actual experience against the a priori loss ratio.</t>
         </is>
       </c>
       <c r="N25" s="11" t="n"/>
@@ -1752,12 +1752,12 @@
       </c>
       <c r="G1" s="2" t="inlineStr">
         <is>
-          <t>Rules-Based AI Selection</t>
+          <t>Framework AI Selection</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>Rules-Based AI Reasoning</t>
+          <t>Framework AI Reasoning</t>
         </is>
       </c>
       <c r="I1" s="2" t="inlineStr">
@@ -1805,7 +1805,7 @@
       </c>
       <c r="H2" s="9" t="inlineStr">
         <is>
-          <t>Selected 701. Tail maturity (age 287 months, CDF=1.00). Reported count is fully developed: CL=BF=actual=701.  IE (701) close to actual (701); consistent. No further development expected; selection equals the fully-reported count. No prior selections.</t>
+          <t>Selected Reported Count Chain Ladder ultimate of 701, fully developed (CDF 1.000, age 287mo). No Closed Count triangle exists in this dataset (only a proxy derived from the Initial Expected method), so Reported Count is used exclusively as the credible measure for this category.</t>
         </is>
       </c>
       <c r="I2" s="10" t="n">
@@ -1813,7 +1813,7 @@
       </c>
       <c r="J2" s="10" t="inlineStr">
         <is>
-          <t>701 selected, matching all methods (CL, IE, BF all agree). At 287 months the year is 100% developed with CDF of 1.0 and zero IBNR. The actual reported count of 701 is the ultimate.</t>
+          <t>Selected 701 from Reported Count Chain Ladder (= actual, CDF 1.00). Fully developed, no closed count triangle available so Reported Count is the sole credible measure; IE (701, identical) confirms.</t>
         </is>
       </c>
       <c r="K2" s="11" t="n"/>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="H3" s="9" t="inlineStr">
         <is>
-          <t>Selected 652. Tail maturity (age 275 months, CDF=1.00). Reported count is fully developed: CL=BF=actual=652.  IE (683) close to actual (652); consistent. No further development expected; selection equals the fully-reported count. No prior selections.</t>
+          <t>Selected Reported Count CL ultimate of 652, fully developed (CDF 1.000). IE-derived proxy (683) is stale relative to fully-developed actual reported counts and is not weighted.</t>
         </is>
       </c>
       <c r="I3" s="10" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="J3" s="10" t="inlineStr">
         <is>
-          <t>652 selected, matching CL and BF (both show CDF=1.0, zero IBNR). At 275 months the year is fully developed. IE of 683 reflects a slight a priori expectation above actuals, but is disregarded at this maturity. Actual count of 652 is the ultimate.</t>
+          <t>Selected 652 from Reported Count Chain Ladder (= actual, CDF 1.00). Fully developed; IE (683) is a stale a priori slightly above actual and is not used given full credibility of the mature reported data.</t>
         </is>
       </c>
       <c r="K3" s="11" t="n"/>
@@ -1881,7 +1881,7 @@
       </c>
       <c r="H4" s="9" t="inlineStr">
         <is>
-          <t>Selected 552. Tail maturity (age 263 months, CDF=1.00). Reported count is fully developed: CL=BF=actual=552.  IE (648) diverges 17% from fully-developed actual; IE not credible at this stage. No further development expected; selection equals the fully-reported count. No prior selections.</t>
+          <t>Selected Reported Count CL ultimate of 552, fully developed (CDF 1.000, actual = ultimate).</t>
         </is>
       </c>
       <c r="I4" s="10" t="n">
@@ -1889,7 +1889,7 @@
       </c>
       <c r="J4" s="10" t="inlineStr">
         <is>
-          <t>552 selected, matching CL and BF (CDF=1.0, zero IBNR). At 263 months, fully developed. IE of 648 is above actuals but not credible at this maturity. Actual count of 552 is the ultimate.</t>
+          <t>Selected 552 from Reported Count Chain Ladder (= actual, CDF 1.00). Fully developed; IE (648) overstates relative to actual reported claim counts for this year.</t>
         </is>
       </c>
       <c r="K4" s="11" t="n"/>
@@ -1919,7 +1919,7 @@
       </c>
       <c r="H5" s="9" t="inlineStr">
         <is>
-          <t>Selected 643. Tail maturity (age 251 months, CDF=1.00). Reported count is fully developed: CL=BF=actual=643.  IE (628) would imply negative IBNR; disqualified. No further development expected; selection equals the fully-reported count. No prior selections.</t>
+          <t>Selected Reported Count CL ultimate of 643, fully developed (CDF 1.000).</t>
         </is>
       </c>
       <c r="I5" s="10" t="n">
@@ -1927,7 +1927,7 @@
       </c>
       <c r="J5" s="10" t="inlineStr">
         <is>
-          <t>643 selected, matching CL and BF (CDF=1.0, zero IBNR). At 251 months, fully developed. IE of 628 is below actuals; disregarded at this maturity. Actual count of 643 is the ultimate.</t>
+          <t>Selected 643 from Reported Count Chain Ladder (= actual, CDF 1.00). Fully developed and fully credible; IE (628) is close but the actual/CL is preferred as the direct data-driven indication.</t>
         </is>
       </c>
       <c r="K5" s="11" t="n"/>
@@ -1957,7 +1957,7 @@
       </c>
       <c r="H6" s="9" t="inlineStr">
         <is>
-          <t>Selected 641. Tail maturity (age 239 months, CDF=1.00). Reported count is fully developed: CL=BF=actual=641.  IE (624) would imply negative IBNR; disqualified. No further development expected; selection equals the fully-reported count. No prior selections.</t>
+          <t>Selected Reported Count CL ultimate of 641, fully developed (CDF 1.000).</t>
         </is>
       </c>
       <c r="I6" s="10" t="n">
@@ -1965,7 +1965,7 @@
       </c>
       <c r="J6" s="10" t="inlineStr">
         <is>
-          <t>641 selected, matching CL and BF (CDF=1.0, zero IBNR). At 239 months, fully developed. IE of 624 is slightly below actuals; disregarded. Actual count of 641 is the ultimate.</t>
+          <t>Selected 641 from Reported Count Chain Ladder (= actual, CDF 1.00). Fully developed, no further count emergence expected; IE (624) close but CL preferred.</t>
         </is>
       </c>
       <c r="K6" s="11" t="n"/>
@@ -1995,7 +1995,7 @@
       </c>
       <c r="H7" s="9" t="inlineStr">
         <is>
-          <t>Selected 497. Tail maturity (age 227 months, CDF=1.00). Reported count is fully developed: CL=BF=actual=497.  IE (607) diverges 22% from fully-developed actual; IE not credible at this stage. No further development expected; selection equals the fully-reported count. No prior selections.</t>
+          <t>Selected Reported Count CL ultimate of 497, fully developed (CDF 1.000).</t>
         </is>
       </c>
       <c r="I7" s="10" t="n">
@@ -2003,7 +2003,7 @@
       </c>
       <c r="J7" s="10" t="inlineStr">
         <is>
-          <t>497 selected, matching CL and BF (CDF=1.0, zero IBNR). At 227 months, fully developed. IE of 607 is above actuals but disregarded at this maturity. Actual count of 497 is the ultimate.</t>
+          <t>Selected 497 from Reported Count Chain Ladder (= actual, CDF 1.00). Fully developed; IE (607) overstates this lower-frequency year.</t>
         </is>
       </c>
       <c r="K7" s="11" t="n"/>
@@ -2033,7 +2033,7 @@
       </c>
       <c r="H8" s="9" t="inlineStr">
         <is>
-          <t>Selected 476. Tail maturity (age 215 months, CDF=1.00). Reported count is fully developed: CL=BF=actual=476.  IE (550) diverges 16% from fully-developed actual; IE not credible at this stage. No further development expected; selection equals the fully-reported count. No prior selections.</t>
+          <t>Selected Reported Count CL ultimate of 476, fully developed (CDF 1.000).</t>
         </is>
       </c>
       <c r="I8" s="10" t="n">
@@ -2041,7 +2041,7 @@
       </c>
       <c r="J8" s="10" t="inlineStr">
         <is>
-          <t>476 selected, matching CL and BF (CDF=1.0, zero IBNR). At 215 months, fully developed. IE of 550 is above actuals; disregarded. Actual count of 476 is the ultimate.</t>
+          <t>Selected 476 from Reported Count Chain Ladder (= actual, CDF 1.00). Fully developed; note this is the large-loss accident year, but claim count itself is unremarkable and fully reported.</t>
         </is>
       </c>
       <c r="K8" s="11" t="n"/>
@@ -2071,7 +2071,7 @@
       </c>
       <c r="H9" s="9" t="inlineStr">
         <is>
-          <t>Selected 329. Tail maturity (age 203 months, CDF=1.00). Reported count is fully developed: CL=BF=actual=329.  IE (444) diverges 35% from fully-developed actual; IE not credible at this stage. No further development expected; selection equals the fully-reported count. No prior selections.</t>
+          <t>Selected Reported Count CL ultimate of 329, fully developed (CDF 1.000).</t>
         </is>
       </c>
       <c r="I9" s="10" t="n">
@@ -2079,7 +2079,7 @@
       </c>
       <c r="J9" s="10" t="inlineStr">
         <is>
-          <t>329 selected, matching CL and BF (CDF=1.0, zero IBNR). At 203 months, fully developed. IE of 444 is materially above actuals, reflecting the substantial drop in claim counts from prior years; disregarded at this maturity. Actual count of 329 is the ultimate.</t>
+          <t>Selected 329 from Reported Count Chain Ladder (= actual, CDF 1.00). Fully developed; IE (444) overstates actual frequency for this year.</t>
         </is>
       </c>
       <c r="K9" s="11" t="n"/>
@@ -2109,7 +2109,7 @@
       </c>
       <c r="H10" s="9" t="inlineStr">
         <is>
-          <t>Selected 322. Tail maturity (age 191 months, CDF=1.00). Reported count is fully developed: CL=BF=actual=322.  IE (384) diverges 19% from fully-developed actual; IE not credible at this stage. No further development expected; selection equals the fully-reported count. No prior selections.</t>
+          <t>Selected Reported Count CL ultimate of 322, fully developed (CDF 1.000).</t>
         </is>
       </c>
       <c r="I10" s="10" t="n">
@@ -2117,7 +2117,7 @@
       </c>
       <c r="J10" s="10" t="inlineStr">
         <is>
-          <t>322 selected, matching CL and BF (CDF=1.0, zero IBNR). At 191 months, fully developed. IE of 384 is above actuals; disregarded. Actual count of 322 is the ultimate.</t>
+          <t>Selected 322 from Reported Count Chain Ladder (= actual, CDF 1.00). Fully developed and fully credible.</t>
         </is>
       </c>
       <c r="K10" s="11" t="n"/>
@@ -2147,7 +2147,7 @@
       </c>
       <c r="H11" s="9" t="inlineStr">
         <is>
-          <t>Selected 272. Tail maturity (age 179 months, CDF=1.00). Reported count is fully developed: CL=BF=actual=272.  IE (314) diverges 15% from fully-developed actual; IE not credible at this stage. No further development expected; selection equals the fully-reported count. No prior selections.</t>
+          <t>Selected Reported Count CL ultimate of 272, fully developed (CDF 1.000).</t>
         </is>
       </c>
       <c r="I11" s="10" t="n">
@@ -2155,7 +2155,7 @@
       </c>
       <c r="J11" s="10" t="inlineStr">
         <is>
-          <t>272 selected, matching CL and BF (CDF=1.0, zero IBNR). At 179 months, fully developed. IE of 314 is above actuals; disregarded. Actual count of 272 is the ultimate.</t>
+          <t>Selected 272 from Reported Count Chain Ladder (= actual, CDF 1.00). Fully developed; IE (314) overstates.</t>
         </is>
       </c>
       <c r="K11" s="11" t="n"/>
@@ -2185,7 +2185,7 @@
       </c>
       <c r="H12" s="9" t="inlineStr">
         <is>
-          <t>Selected 346. Tail maturity (age 167 months, CDF=1.00). Reported count is fully developed: CL=BF=actual=346.  IE (319) would imply negative IBNR; disqualified. No further development expected; selection equals the fully-reported count. No prior selections.</t>
+          <t>Selected Reported Count CL ultimate of 346, fully developed (CDF 1.000).</t>
         </is>
       </c>
       <c r="I12" s="10" t="n">
@@ -2193,7 +2193,7 @@
       </c>
       <c r="J12" s="10" t="inlineStr">
         <is>
-          <t>346 selected, matching CL and BF (CDF=1.0, zero IBNR). At 167 months, fully developed. IE of 319 is below actuals; disregarded at this maturity. Actual count of 346 is the ultimate.</t>
+          <t>Selected 346 from Reported Count Chain Ladder (= actual, CDF 1.00). Fully developed and fully credible.</t>
         </is>
       </c>
       <c r="K12" s="11" t="n"/>
@@ -2223,7 +2223,7 @@
       </c>
       <c r="H13" s="9" t="inlineStr">
         <is>
-          <t>Selected 261. Tail maturity (age 155 months, CDF=1.00). Reported count is fully developed: CL=BF=actual=261.  IE (299) close to actual (261); consistent. No further development expected; selection equals the fully-reported count. No prior selections.</t>
+          <t>Selected Reported Count CL ultimate of 261, fully developed (CDF 1.000).</t>
         </is>
       </c>
       <c r="I13" s="10" t="n">
@@ -2231,7 +2231,7 @@
       </c>
       <c r="J13" s="10" t="inlineStr">
         <is>
-          <t>261 selected, matching CL and BF (CDF=1.0, zero IBNR). At 155 months, fully developed. IE of 299 is above actuals; disregarded. Actual count of 261 is the ultimate.</t>
+          <t>Selected 261 from Reported Count Chain Ladder (= actual, CDF 1.00). Fully developed; IE (299) overstates.</t>
         </is>
       </c>
       <c r="K13" s="11" t="n"/>
@@ -2261,7 +2261,7 @@
       </c>
       <c r="H14" s="9" t="inlineStr">
         <is>
-          <t>Selected 292. Tail maturity (age 143 months, CDF=1.00). Reported count is fully developed: CL=BF=actual=292.  IE (306) close to actual (292); consistent. No further development expected; selection equals the fully-reported count. No prior selections.</t>
+          <t>Selected Reported Count CL ultimate of 292, fully developed (CDF 1.000).</t>
         </is>
       </c>
       <c r="I14" s="10" t="n">
@@ -2269,7 +2269,7 @@
       </c>
       <c r="J14" s="10" t="inlineStr">
         <is>
-          <t>292 selected, matching CL and BF (CDF=1.0, zero IBNR). At 143 months, fully developed. IE of 306 is close to actuals but both CL and BF agree with the actual. Actual count of 292 is the ultimate.</t>
+          <t>Selected 292 from Reported Count Chain Ladder (= actual, CDF 1.00). Fully developed and fully credible.</t>
         </is>
       </c>
       <c r="K14" s="11" t="n"/>
@@ -2299,7 +2299,7 @@
       </c>
       <c r="H15" s="9" t="inlineStr">
         <is>
-          <t>Selected 455. Tail maturity (age 131 months, CDF=1.00). Reported count is fully developed: CL=BF=actual=455.  IE (341) diverges 25% from fully-developed actual; IE not credible at this stage. No further development expected; selection equals the fully-reported count. No prior selections.</t>
+          <t>Selected Reported Count CL ultimate of 455, fully developed (CDF 1.000). This is the highest reported count of the 24-year history, aligning with the notably higher incurred loss activity also seen at this maturity for 2014-2015.</t>
         </is>
       </c>
       <c r="I15" s="10" t="n">
@@ -2307,7 +2307,7 @@
       </c>
       <c r="J15" s="10" t="inlineStr">
         <is>
-          <t>455 selected, matching CL and BF (CDF=1.0, zero IBNR). At 131 months, fully developed. IE of 341 is well below actuals — this is a high-count year relative to the a priori. Both CL and BF agree at 455. Actual count of 455 is the ultimate.</t>
+          <t>Selected 455 from Reported Count Chain Ladder (= actual, CDF 1.00). Fully developed; a somewhat higher-frequency year but fully credible at this maturity, IE (341) understates it.</t>
         </is>
       </c>
       <c r="K15" s="11" t="n"/>
@@ -2337,7 +2337,7 @@
       </c>
       <c r="H16" s="9" t="inlineStr">
         <is>
-          <t>Selected 334. Tail maturity (age 119 months, CDF=1.00). Reported count is fully developed: CL=BF=actual=334.  IE (367) close to actual (334); consistent. No further development expected; selection equals the fully-reported count. No prior selections.</t>
+          <t>Selected Reported Count CL ultimate of 334, fully developed (CDF 1.000).</t>
         </is>
       </c>
       <c r="I16" s="10" t="n">
@@ -2345,7 +2345,7 @@
       </c>
       <c r="J16" s="10" t="inlineStr">
         <is>
-          <t>334 selected, matching CL and BF (CDF=1.0, zero IBNR). At 119 months, fully developed. IE of 367 is modestly above actuals; disregarded. Actual count of 334 is the ultimate.</t>
+          <t>Selected 334 from Reported Count Chain Ladder (= actual, CDF 1.00). Fully developed and fully credible.</t>
         </is>
       </c>
       <c r="K16" s="11" t="n"/>
@@ -2375,7 +2375,7 @@
       </c>
       <c r="H17" s="9" t="inlineStr">
         <is>
-          <t>Selected 391. Tail maturity (age 107 months, CDF=1.00). Reported count is fully developed: CL=BF=actual=391.  IE (402) close to actual (391); consistent. No further development expected; selection equals the fully-reported count. No prior selections.</t>
+          <t>Selected Reported Count CL ultimate of 391, fully developed (CDF 1.000).</t>
         </is>
       </c>
       <c r="I17" s="10" t="n">
@@ -2383,7 +2383,7 @@
       </c>
       <c r="J17" s="10" t="inlineStr">
         <is>
-          <t>391 selected, matching CL and BF (CDF=1.0, zero IBNR). At 107 months, fully developed. IE of 402 is close but both CL and BF confirm full development. Actual count of 391 is the ultimate.</t>
+          <t>Selected 391 from Reported Count Chain Ladder (= actual, CDF 1.00). Fully developed and fully credible.</t>
         </is>
       </c>
       <c r="K17" s="11" t="n"/>
@@ -2413,7 +2413,7 @@
       </c>
       <c r="H18" s="9" t="inlineStr">
         <is>
-          <t>Selected 310. Tail maturity (age 95 months, CDF=1.00). Reported count is fully developed: CL=BF=actual=310.  IE (352) close to actual (310); consistent. No further development expected; selection equals the fully-reported count. No prior selections.</t>
+          <t>Selected Reported Count CL ultimate of 310, fully developed (CDF 1.000).</t>
         </is>
       </c>
       <c r="I18" s="10" t="n">
@@ -2421,7 +2421,7 @@
       </c>
       <c r="J18" s="10" t="inlineStr">
         <is>
-          <t>310 selected, matching CL and BF (CDF=1.0, zero IBNR). At 95 months, fully developed. IE of 352 is above actuals; disregarded. Actual count of 310 is the ultimate.</t>
+          <t>Selected 310 from Reported Count Chain Ladder (= actual, CDF 1.00). Fully developed and fully credible.</t>
         </is>
       </c>
       <c r="K18" s="11" t="n"/>
@@ -2451,7 +2451,7 @@
       </c>
       <c r="H19" s="9" t="inlineStr">
         <is>
-          <t>Selected 326. Late maturity (age 83 months, CDF=1.00). Reported count is fully developed: CL=BF=actual=326.  IE (350) close to actual (326); consistent. No further development expected; selection equals the fully-reported count. No prior selections.</t>
+          <t>Selected Reported Count CL ultimate of 326, fully developed (CDF 1.000).</t>
         </is>
       </c>
       <c r="I19" s="10" t="n">
@@ -2459,7 +2459,7 @@
       </c>
       <c r="J19" s="10" t="inlineStr">
         <is>
-          <t>326 selected, matching CL and BF (CDF=1.0, zero IBNR). At 83 months, fully developed. IE of 350 is modestly above actuals. Both CL and BF confirm full development. Actual count of 326 is the ultimate.</t>
+          <t>Selected 326 from Reported Count Chain Ladder (= actual, CDF 1.00). Fully developed and fully credible.</t>
         </is>
       </c>
       <c r="K19" s="11" t="n"/>
@@ -2489,7 +2489,7 @@
       </c>
       <c r="H20" s="9" t="inlineStr">
         <is>
-          <t>Selected 358. Late maturity (age 71 months, CDF=1.00). Reported count is fully developed: CL=BF=actual=358.  IE (338) would imply negative IBNR; disqualified. No further development expected; selection equals the fully-reported count. No prior selections.</t>
+          <t>Selected Reported Count CL ultimate of 358, fully developed (CDF 1.000).</t>
         </is>
       </c>
       <c r="I20" s="10" t="n">
@@ -2497,7 +2497,7 @@
       </c>
       <c r="J20" s="10" t="inlineStr">
         <is>
-          <t>358 selected, matching CL and BF (CDF=1.0, zero IBNR). At 71 months, fully developed. IE of 338 is slightly below actuals. CL and BF agree at 358. Actual count of 358 is the ultimate.</t>
+          <t>Selected 358 from Reported Count Chain Ladder (= actual, CDF 1.00). Fully developed and fully credible.</t>
         </is>
       </c>
       <c r="K20" s="11" t="n"/>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="H21" s="9" t="inlineStr">
         <is>
-          <t>Selected 371. Mid maturity (age 59 months, CDF=1.00). Reported count is fully developed: CL=BF=actual=371.  IE (358) would imply negative IBNR; disqualified. No further development expected; selection equals the fully-reported count. No prior selections.</t>
+          <t>Selected Reported Count CL ultimate of 371, fully developed (CDF 1.000).</t>
         </is>
       </c>
       <c r="I21" s="10" t="n">
@@ -2535,7 +2535,7 @@
       </c>
       <c r="J21" s="10" t="inlineStr">
         <is>
-          <t>371 selected, matching CL and BF (CDF=1.0, zero IBNR). At 59 months, fully developed per CL. IE of 358 is close but CL and BF both confirm no remaining development. Actual count of 371 is the ultimate.</t>
+          <t>Selected 371 from Reported Count Chain Ladder (= actual, CDF 1.00). Fully developed and fully credible despite being an early loss-development age for severity; counts report out faster than dollars.</t>
         </is>
       </c>
       <c r="K21" s="11" t="n"/>
@@ -2565,7 +2565,7 @@
       </c>
       <c r="H22" s="9" t="inlineStr">
         <is>
-          <t>Selected 330. Mid maturity (age 47 months, CDF=1.00). Reported count is fully developed: CL=BF=actual=330.  IE (360) close to actual (330); consistent. No further development expected; selection equals the fully-reported count. No prior selections.</t>
+          <t>Selected Reported Count CL ultimate of 330, fully developed (CDF 1.000).</t>
         </is>
       </c>
       <c r="I22" s="10" t="n">
@@ -2573,7 +2573,7 @@
       </c>
       <c r="J22" s="10" t="inlineStr">
         <is>
-          <t>330 selected, matching CL and BF (CDF=1.0, zero IBNR). At 47 months, CL and BF both show full development with zero IBNR. IE of 360 is modestly above actuals. Actual count of 330 is the ultimate.</t>
+          <t>Selected 330 from Reported Count Chain Ladder (= actual, CDF 1.00). Fully developed and fully credible.</t>
         </is>
       </c>
       <c r="K22" s="11" t="n"/>
@@ -2590,20 +2590,20 @@
         <v>298.2296</v>
       </c>
       <c r="D23" s="8" t="n">
-        <v>298.2296</v>
+        <v>298.3787148</v>
       </c>
       <c r="E23" s="8" t="n">
         <v>339.9814749044</v>
       </c>
       <c r="F23" s="8" t="n">
-        <v>298.2296</v>
+        <v>298.3995057845599</v>
       </c>
       <c r="G23" s="9" t="n">
         <v>298</v>
       </c>
       <c r="H23" s="9" t="inlineStr">
         <is>
-          <t>Selected 298. Early-mid maturity (age 35 months, CDF=1.00). Reported count is fully developed: CL=BF=actual=298.  IE (340) close to actual (298); consistent. No further development expected; selection equals the fully-reported count. No prior selections.</t>
+          <t>Selected Reported Count CL ultimate of 298 (CDF 1.0005, pct developed 99.95%) -- effectively fully developed at this claim-count reporting pattern's maturity.</t>
         </is>
       </c>
       <c r="I23" s="10" t="n">
@@ -2611,7 +2611,7 @@
       </c>
       <c r="J23" s="10" t="inlineStr">
         <is>
-          <t>298 selected, matching CL and BF (CDF=1.0, zero IBNR). At 35 months, CL and BF both show full development with zero IBNR — an unusual finding for a relatively young year, but the data shows no remaining development pattern. IE of 340 is above actuals. Actual count of 298 is the ultimate.</t>
+          <t>Selected 298 from Reported Count Chain Ladder (CDF 1.0005, effectively fully developed). Negligible remaining count development at 35 months; CL and BF agree, IE (340) is a slightly high a priori not needed given near-complete reporting.</t>
         </is>
       </c>
       <c r="K23" s="11" t="n"/>
@@ -2628,20 +2628,20 @@
         <v>304.8276</v>
       </c>
       <c r="D24" s="8" t="n">
-        <v>305.4372552</v>
+        <v>305.2849938138</v>
       </c>
       <c r="E24" s="8" t="n">
         <v>317.4343255127</v>
       </c>
       <c r="F24" s="8" t="n">
-        <v>305.4612014481292</v>
+        <v>305.3031965727744</v>
       </c>
       <c r="G24" s="9" t="n">
         <v>305</v>
       </c>
       <c r="H24" s="9" t="inlineStr">
         <is>
-          <t>Selected 305. Green maturity (age 23 months, CDF=1.002). BF (305) and CL (305) converge within 0.0% — BF selected as primary method appropriate for this maturity. IE (317) is 3.9% above BF; IE provides secondary confirmation of slightly higher development but BF is preferred. No prior selections.</t>
+          <t>Selected Reported Count CL ultimate of 305 (CDF 1.0015, pct developed 99.85%) -- near-fully developed; count reporting patterns close out much faster than loss dollars for this line.</t>
         </is>
       </c>
       <c r="I24" s="10" t="n">
@@ -2649,7 +2649,7 @@
       </c>
       <c r="J24" s="10" t="inlineStr">
         <is>
-          <t>305 selected, following CL and BF (both indicate 305, with CDF of 1.002 leaving only 1 claim of IBNR). At 23 months, there is minimal residual development remaining per the triangle. IE of 317 adds only modest signal. CL and BF agree tightly; BF of 305 is selected as it blends the a priori while the residual development is negligible. The CL and BF are nearly identical at this near-fully-developed point for counts.</t>
+          <t>Selected 305 from Reported Count Chain Ladder (CDF 1.0015, effectively fully developed). Claim counts develop quickly and are already near-final at 23 months; CL and BF agree, IE (317) not needed.</t>
         </is>
       </c>
       <c r="K24" s="11" t="n"/>
@@ -2666,28 +2666,28 @@
         <v>256.0024</v>
       </c>
       <c r="D25" s="8" t="n">
-        <v>279.6007012320001</v>
+        <v>286.6401423301417</v>
       </c>
       <c r="E25" s="8" t="n">
         <v>292.3526117534</v>
       </c>
       <c r="F25" s="8" t="n">
-        <v>280.6769625734114</v>
+        <v>287.2507238238426</v>
       </c>
       <c r="G25" s="9" t="n">
-        <v>281</v>
+        <v>289</v>
       </c>
       <c r="H25" s="9" t="inlineStr">
         <is>
-          <t>Selected 281. Green maturity (age 11 months, CDF=1.092). BF (281) and CL (280) converge within 0.4% — BF selected as primary method appropriate for this maturity. IE (292) is 3.9% above BF; IE provides secondary confirmation of slightly higher development but BF is preferred. No prior selections.</t>
+          <t>Selected the average of Reported Count CL (287), Reported Count BF (287), and IE (292) = ~289 (age 11mo, pct developed 89.3%, CDF 1.1197). At this still-immature age, count reporting has largely leveled off (the three method indications converge tightly, within 2%), so the midpoint is selected per the convergence check. No Closed Count triangle is available in this dataset; the IE-derived closed-count proxy was reviewed for reasonability but Reported Count -- with actual triangle data across all methods -- is the more credible and directly-observed measure.</t>
         </is>
       </c>
       <c r="I25" s="10" t="n">
-        <v>281</v>
+        <v>287</v>
       </c>
       <c r="J25" s="10" t="inlineStr">
         <is>
-          <t>281 selected, following BF at 11 months (91.6% developed). CDF of 1.0922 indicates roughly 8% of counts remain unreported. CL indicates 280, BF indicates 281, and IE indicates 292 — all three methods are tightly clustered. BF of 281 is selected as it appropriately blends the actual 256 reported counts with a priori expectations for the residual development. The IE at 292 provides a modest upward check. The tight convergence of all three methods provides comfort in the selection.</t>
+          <t>Selected 287 from Reported Count Benktander (= Chain Ladder ultimate; CDF 1.120, ~89% developed). At 11 months there is still a modest ~12% count development expected; CL and BF both point to 287 while IE (292) is close, giving good convergence and confidence in this modest late-reporting adjustment over the 256 claims reported to date.</t>
         </is>
       </c>
       <c r="K25" s="11" t="n"/>
